--- a/reports/Group/Planning-Template.xlsx
+++ b/reports/Group/Planning-Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPOSM\my\2C\dp2\proyecto\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPOSM\my\2C\dp2\workspace\Workspace-26\Projects\Acme-Starters-B\reports\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EFCD65-4D08-4FE8-AA27-9C289B796D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFC2F4F-3145-4B6B-A003-862E26C67CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="10" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="207">
   <si>
     <t xml:space="preserve">  Enter configuration data in these cells</t>
   </si>
@@ -593,6 +593,93 @@
   </si>
   <si>
     <t>Check D1 In EV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> L04 – Formal testing-S01 – Functional testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> L04 – Formal testing-S02 – Performance testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> L04 – Formal testing-S03 – Advanced topics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L05 – Miscellaneous topics-S01 – Workshop </t>
+  </si>
+  <si>
+    <t>Workshop Presentations</t>
+  </si>
+  <si>
+    <t>Design the relational model</t>
+  </si>
+  <si>
+    <t>Write questions, possible solutions and chosen option</t>
+  </si>
+  <si>
+    <t>Obtain / update Manager role.</t>
+  </si>
+  <si>
+    <t>Create / list projects.</t>
+  </si>
+  <si>
+    <t>Show and update a project.</t>
+  </si>
+  <si>
+    <t>Add Sample data ( Manager and ProjectSquad ).</t>
+  </si>
+  <si>
+    <t>Implement Dashboard model.</t>
+  </si>
+  <si>
+    <t>Implement Project , Managar , ProjectSquad, components model.</t>
+  </si>
+  <si>
+    <t>Implement banner model, service, controller, UI.</t>
+  </si>
+  <si>
+    <t>Implement sponsorship, auditReport link with project, UI, model, service, controller.</t>
+  </si>
+  <si>
+    <t>Implement list and show projects (Any role).</t>
+  </si>
+  <si>
+    <t>Implement effort and TotalActiveMonths update  (update / publish / delete / assign in components).</t>
+  </si>
+  <si>
+    <t>Delete project.</t>
+  </si>
+  <si>
+    <t>Publish project.</t>
+  </si>
+  <si>
+    <t>Implement list and show Inventios (Project-squad role).</t>
+  </si>
+  <si>
+    <t>List member.</t>
+  </si>
+  <si>
+    <t>List member (Any role).</t>
+  </si>
+  <si>
+    <t>Assign / unlink components.</t>
+  </si>
+  <si>
+    <t>List spokespeople, fundrasisers, inventors thar aren't in the project.</t>
+  </si>
+  <si>
+    <t>List show campaigns, strategies.</t>
+  </si>
+  <si>
+    <t>List show sponsorship, donations.</t>
+  </si>
+  <si>
+    <t>Implement Dashboard service and controller.</t>
+  </si>
+  <si>
+    <t>Add Sample / Error data ( Project and Memeber ).</t>
+  </si>
+  <si>
+    <t>List show auditReport , AuditSection</t>
   </si>
 </sst>
 </file>
@@ -6572,7 +6659,7 @@
       </c>
       <c r="K101" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Planned</v>
+        <v>Completed</v>
       </c>
       <c r="L101" s="47">
         <v>1.87</v>
@@ -6621,7 +6708,7 @@
       </c>
       <c r="K102" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Planned</v>
+        <v>Completed</v>
       </c>
       <c r="L102" s="47">
         <v>0.5</v>
@@ -6670,7 +6757,7 @@
       </c>
       <c r="K103" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Planned</v>
+        <v>Completed</v>
       </c>
       <c r="L103" s="47">
         <v>0.25</v>
@@ -6721,7 +6808,7 @@
       </c>
       <c r="K104" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Planned</v>
+        <v>Completed</v>
       </c>
       <c r="L104" s="47">
         <v>1</v>
@@ -6772,7 +6859,7 @@
       </c>
       <c r="K105" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Planned</v>
+        <v>Completed</v>
       </c>
       <c r="L105" s="47">
         <v>1</v>
@@ -6823,7 +6910,7 @@
       </c>
       <c r="K106" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Planned</v>
+        <v>Completed</v>
       </c>
       <c r="L106" s="47">
         <v>0.33</v>
@@ -7058,7 +7145,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.5546875" customWidth="1"/>
+    <col min="16" max="16" width="96.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
@@ -7122,7 +7209,7 @@
       </c>
       <c r="E6" s="35">
         <f>SUM(N11:N110)</f>
-        <v>0</v>
+        <v>1157.75</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -7143,7 +7230,7 @@
       </c>
       <c r="E7" s="36">
         <f>SUM(O11:O110)</f>
-        <v>0</v>
+        <v>1146.5</v>
       </c>
       <c r="J7" s="37"/>
     </row>
@@ -7223,30 +7310,48 @@
       </c>
       <c r="C11" s="42" t="str">
         <f>IF(ISBLANK(D11), "", _xlfn.CONCAT("T", TEXT(B11, "0000"), "/", VLOOKUP(D11, Internal!$B$35:C$39, 2, FALSE), IF(OR(D11="QA", D11="Revision"), _xlfn.CONCAT("/", H11), "")))</f>
-        <v/>
-      </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="44"/>
+        <v>T0001/O</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>30</v>
+      </c>
       <c r="H11" s="43"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
+      <c r="I11" s="46">
+        <v>46118.444444444445</v>
+      </c>
+      <c r="J11" s="46">
+        <v>46118.520833333336</v>
+      </c>
       <c r="K11" s="45" t="str">
         <f ca="1">IF(OR(I11="",J11=""),"",IF(AND(J11&lt;&gt;"",I11&gt;=NOW()),"Planned",IF(AND(J11&lt;&gt;"",J11&lt;NOW()),"Completed","Ongoing")))</f>
-        <v/>
-      </c>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L11" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="M11" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="N11" s="45">
         <f>IF(ISBLANK(L11), "", L11*VLOOKUP($F11,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O11" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O11" s="45">
         <f>IF(ISBLANK(M11), "", M11*VLOOKUP($F11,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P11" s="44"/>
+        <v>0</v>
+      </c>
+      <c r="P11" s="44" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="41">
@@ -7254,30 +7359,48 @@
       </c>
       <c r="C12" s="42" t="str">
         <f>IF(ISBLANK(D12), "", _xlfn.CONCAT("T", TEXT(B12, "0000"), "/", VLOOKUP(D12, Internal!$B$35:C$39, 2, FALSE), IF(OR(D12="QA", D12="Revision"), _xlfn.CONCAT("/", H12), "")))</f>
-        <v/>
-      </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="44"/>
+        <v>T0002/O</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="44" t="s">
+        <v>30</v>
+      </c>
       <c r="H12" s="43"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
+      <c r="I12" s="46">
+        <v>46121.354166666664</v>
+      </c>
+      <c r="J12" s="46">
+        <v>46121.430555555555</v>
+      </c>
       <c r="K12" s="45" t="str">
         <f t="shared" ref="K12:K75" ca="1" si="0">IF(OR(I12="",J12=""),"",IF(AND(J12&lt;&gt;"",I12&gt;=NOW()),"Planned",IF(AND(J12&lt;&gt;"",J12&lt;NOW()),"Completed","Ongoing")))</f>
-        <v/>
-      </c>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L12" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="M12" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="N12" s="45">
         <f>IF(ISBLANK(L12), "", L12*VLOOKUP($F12,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O12" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O12" s="45">
         <f>IF(ISBLANK(M12), "", M12*VLOOKUP($F12,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P12" s="44"/>
+        <v>0</v>
+      </c>
+      <c r="P12" s="44" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="41">
@@ -7285,30 +7408,48 @@
       </c>
       <c r="C13" s="42" t="str">
         <f>IF(ISBLANK(D13), "", _xlfn.CONCAT("T", TEXT(B13, "0000"), "/", VLOOKUP(D13, Internal!$B$35:C$39, 2, FALSE), IF(OR(D13="QA", D13="Revision"), _xlfn.CONCAT("/", H13), "")))</f>
-        <v/>
-      </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="44"/>
+        <v>T0003/O</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>30</v>
+      </c>
       <c r="H13" s="43"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
+      <c r="I13" s="46">
+        <v>46125.444444444445</v>
+      </c>
+      <c r="J13" s="46">
+        <v>46125.520833333336</v>
+      </c>
       <c r="K13" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L13" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="M13" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="N13" s="45">
         <f>IF(ISBLANK(L13), "", L13*VLOOKUP($F13,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O13" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O13" s="45">
         <f>IF(ISBLANK(M13), "", M13*VLOOKUP($F13,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P13" s="44"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="44" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="41">
@@ -7316,30 +7457,48 @@
       </c>
       <c r="C14" s="42" t="str">
         <f>IF(ISBLANK(D14), "", _xlfn.CONCAT("T", TEXT(B14, "0000"), "/", VLOOKUP(D14, Internal!$B$35:C$39, 2, FALSE), IF(OR(D14="QA", D14="Revision"), _xlfn.CONCAT("/", H14), "")))</f>
-        <v/>
-      </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="44"/>
+        <v>T0004/O</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>30</v>
+      </c>
       <c r="H14" s="43"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
+      <c r="I14" s="46">
+        <v>46128.354166666664</v>
+      </c>
+      <c r="J14" s="46">
+        <v>46128.430555555555</v>
+      </c>
       <c r="K14" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L14" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="M14" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="N14" s="45">
         <f>IF(ISBLANK(L14), "", L14*VLOOKUP($F14,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O14" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O14" s="45">
         <f>IF(ISBLANK(M14), "", M14*VLOOKUP($F14,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P14" s="44"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="44" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="41">
@@ -7347,30 +7506,48 @@
       </c>
       <c r="C15" s="42" t="str">
         <f>IF(ISBLANK(D15), "", _xlfn.CONCAT("T", TEXT(B15, "0000"), "/", VLOOKUP(D15, Internal!$B$35:C$39, 2, FALSE), IF(OR(D15="QA", D15="Revision"), _xlfn.CONCAT("/", H15), "")))</f>
-        <v/>
-      </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="44"/>
+        <v>T0005/O</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>30</v>
+      </c>
       <c r="H15" s="43"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
+      <c r="I15" s="46">
+        <v>46139.444444444445</v>
+      </c>
+      <c r="J15" s="46">
+        <v>46139.520833333336</v>
+      </c>
       <c r="K15" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L15" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="M15" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="N15" s="45">
         <f>IF(ISBLANK(L15), "", L15*VLOOKUP($F15,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O15" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O15" s="45">
         <f>IF(ISBLANK(M15), "", M15*VLOOKUP($F15,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P15" s="44"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="44" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="41">
@@ -7378,30 +7555,48 @@
       </c>
       <c r="C16" s="42" t="str">
         <f>IF(ISBLANK(D16), "", _xlfn.CONCAT("T", TEXT(B16, "0000"), "/", VLOOKUP(D16, Internal!$B$35:C$39, 2, FALSE), IF(OR(D16="QA", D16="Revision"), _xlfn.CONCAT("/", H16), "")))</f>
-        <v/>
-      </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="44"/>
+        <v>T0006/O</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>30</v>
+      </c>
       <c r="H16" s="43"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
+      <c r="I16" s="46">
+        <v>46142.354166666664</v>
+      </c>
+      <c r="J16" s="46">
+        <v>46142.430555555555</v>
+      </c>
       <c r="K16" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L16" s="47"/>
-      <c r="M16" s="47"/>
-      <c r="N16" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L16" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="M16" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="N16" s="45">
         <f>IF(ISBLANK(L16), "", L16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O16" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O16" s="45">
         <f>IF(ISBLANK(M16), "", M16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P16" s="44"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="44" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="41">
@@ -7409,30 +7604,48 @@
       </c>
       <c r="C17" s="42" t="str">
         <f>IF(ISBLANK(D17), "", _xlfn.CONCAT("T", TEXT(B17, "0000"), "/", VLOOKUP(D17, Internal!$B$35:C$39, 2, FALSE), IF(OR(D17="QA", D17="Revision"), _xlfn.CONCAT("/", H17), "")))</f>
-        <v/>
-      </c>
-      <c r="D17" s="44"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="44"/>
+        <v>T0007/O</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>30</v>
+      </c>
       <c r="H17" s="43"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
+      <c r="I17" s="46">
+        <v>46146.444444444445</v>
+      </c>
+      <c r="J17" s="46">
+        <v>46146.520833333336</v>
+      </c>
       <c r="K17" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L17" s="47"/>
-      <c r="M17" s="47"/>
-      <c r="N17" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L17" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="M17" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="N17" s="45">
         <f>IF(ISBLANK(L17), "", L17*VLOOKUP($F17,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O17" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O17" s="45">
         <f>IF(ISBLANK(M17), "", M17*VLOOKUP($F17,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P17" s="44"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="44" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="41">
@@ -7440,30 +7653,48 @@
       </c>
       <c r="C18" s="42" t="str">
         <f>IF(ISBLANK(D18), "", _xlfn.CONCAT("T", TEXT(B18, "0000"), "/", VLOOKUP(D18, Internal!$B$35:C$39, 2, FALSE), IF(OR(D18="QA", D18="Revision"), _xlfn.CONCAT("/", H18), "")))</f>
-        <v/>
-      </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="44"/>
+        <v>T0008/O</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>30</v>
+      </c>
       <c r="H18" s="43"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
+      <c r="I18" s="46">
+        <v>46119.354166666664</v>
+      </c>
+      <c r="J18" s="46">
+        <v>46119.430555555555</v>
+      </c>
       <c r="K18" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L18" s="47"/>
-      <c r="M18" s="47"/>
-      <c r="N18" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L18" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="M18" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="N18" s="45">
         <f>IF(ISBLANK(L18), "", L18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O18" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="O18" s="45">
         <f>IF(ISBLANK(M18), "", M18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P18" s="44"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="44" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="41">
@@ -7471,30 +7702,48 @@
       </c>
       <c r="C19" s="42" t="str">
         <f>IF(ISBLANK(D19), "", _xlfn.CONCAT("T", TEXT(B19, "0000"), "/", VLOOKUP(D19, Internal!$B$35:C$39, 2, FALSE), IF(OR(D19="QA", D19="Revision"), _xlfn.CONCAT("/", H19), "")))</f>
-        <v/>
-      </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="44"/>
+        <v>T0009/D</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>37</v>
+      </c>
       <c r="H19" s="43"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
+      <c r="I19" s="46">
+        <v>46124</v>
+      </c>
+      <c r="J19" s="46">
+        <v>46124.999305555553</v>
+      </c>
       <c r="K19" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L19" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="M19" s="47">
+        <v>1</v>
+      </c>
+      <c r="N19" s="45">
         <f>IF(ISBLANK(L19), "", L19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O19" s="45" t="str">
+        <v>60</v>
+      </c>
+      <c r="O19" s="45">
         <f>IF(ISBLANK(M19), "", M19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P19" s="44"/>
+        <v>40</v>
+      </c>
+      <c r="P19" s="44" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="41">
@@ -7502,30 +7751,48 @@
       </c>
       <c r="C20" s="42" t="str">
         <f>IF(ISBLANK(D20), "", _xlfn.CONCAT("T", TEXT(B20, "0000"), "/", VLOOKUP(D20, Internal!$B$35:C$39, 2, FALSE), IF(OR(D20="QA", D20="Revision"), _xlfn.CONCAT("/", H20), "")))</f>
-        <v/>
-      </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="44"/>
+        <v>T0010/D</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>36</v>
+      </c>
       <c r="H20" s="43"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
+      <c r="I20" s="46">
+        <v>46138</v>
+      </c>
+      <c r="J20" s="46">
+        <v>46139.444444444445</v>
+      </c>
       <c r="K20" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L20" s="47"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L20" s="47">
+        <v>2.5</v>
+      </c>
+      <c r="M20" s="47">
+        <v>3</v>
+      </c>
+      <c r="N20" s="45">
         <f>IF(ISBLANK(L20), "", L20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O20" s="45" t="str">
+        <v>100</v>
+      </c>
+      <c r="O20" s="45">
         <f>IF(ISBLANK(M20), "", M20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P20" s="44"/>
+        <v>120</v>
+      </c>
+      <c r="P20" s="44" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="41">
@@ -7533,30 +7800,48 @@
       </c>
       <c r="C21" s="42" t="str">
         <f>IF(ISBLANK(D21), "", _xlfn.CONCAT("T", TEXT(B21, "0000"), "/", VLOOKUP(D21, Internal!$B$35:C$39, 2, FALSE), IF(OR(D21="QA", D21="Revision"), _xlfn.CONCAT("/", H21), "")))</f>
-        <v/>
-      </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="44"/>
+        <v>T0011/D</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H21" s="43"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
+      <c r="I21" s="46">
+        <v>46139.520833333336</v>
+      </c>
+      <c r="J21" s="46">
+        <v>46139.999305555553</v>
+      </c>
       <c r="K21" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L21" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M21" s="47">
+        <v>0.45</v>
+      </c>
+      <c r="N21" s="45">
         <f>IF(ISBLANK(L21), "", L21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O21" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O21" s="45">
         <f>IF(ISBLANK(M21), "", M21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P21" s="44"/>
+        <v>11.25</v>
+      </c>
+      <c r="P21" s="44" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="41">
@@ -7564,30 +7849,48 @@
       </c>
       <c r="C22" s="42" t="str">
         <f>IF(ISBLANK(D22), "", _xlfn.CONCAT("T", TEXT(B22, "0000"), "/", VLOOKUP(D22, Internal!$B$35:C$39, 2, FALSE), IF(OR(D22="QA", D22="Revision"), _xlfn.CONCAT("/", H22), "")))</f>
-        <v/>
-      </c>
-      <c r="D22" s="44"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="44"/>
+        <v>T0012/D</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H22" s="43"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
+      <c r="I22" s="46">
+        <v>46139.520833333336</v>
+      </c>
+      <c r="J22" s="46">
+        <v>46140.645833333336</v>
+      </c>
       <c r="K22" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L22" s="47"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L22" s="47">
+        <v>2.5</v>
+      </c>
+      <c r="M22" s="47">
+        <v>3.15</v>
+      </c>
+      <c r="N22" s="45">
         <f>IF(ISBLANK(L22), "", L22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O22" s="45" t="str">
+        <v>62.5</v>
+      </c>
+      <c r="O22" s="45">
         <f>IF(ISBLANK(M22), "", M22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P22" s="44"/>
+        <v>78.75</v>
+      </c>
+      <c r="P22" s="44" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="41">
@@ -7595,30 +7898,48 @@
       </c>
       <c r="C23" s="42" t="str">
         <f>IF(ISBLANK(D23), "", _xlfn.CONCAT("T", TEXT(B23, "0000"), "/", VLOOKUP(D23, Internal!$B$35:C$39, 2, FALSE), IF(OR(D23="QA", D23="Revision"), _xlfn.CONCAT("/", H23), "")))</f>
-        <v/>
-      </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="44"/>
+        <v>T0013/D</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H23" s="43"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
+      <c r="I23" s="46">
+        <v>46140.645833333336</v>
+      </c>
+      <c r="J23" s="46">
+        <v>46140.999305555553</v>
+      </c>
       <c r="K23" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L23" s="47">
+        <v>2</v>
+      </c>
+      <c r="M23" s="47">
+        <v>2.23</v>
+      </c>
+      <c r="N23" s="45">
         <f>IF(ISBLANK(L23), "", L23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O23" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O23" s="45">
         <f>IF(ISBLANK(M23), "", M23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P23" s="44"/>
+        <v>55.75</v>
+      </c>
+      <c r="P23" s="44" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="41">
@@ -7626,30 +7947,48 @@
       </c>
       <c r="C24" s="42" t="str">
         <f>IF(ISBLANK(D24), "", _xlfn.CONCAT("T", TEXT(B24, "0000"), "/", VLOOKUP(D24, Internal!$B$35:C$39, 2, FALSE), IF(OR(D24="QA", D24="Revision"), _xlfn.CONCAT("/", H24), "")))</f>
-        <v/>
-      </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="44"/>
+        <v>T0014/D</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H24" s="43"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
+      <c r="I24" s="46">
+        <v>46140.645833333336</v>
+      </c>
+      <c r="J24" s="46">
+        <v>46140.999305555553</v>
+      </c>
       <c r="K24" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L24" s="47">
+        <v>0.75</v>
+      </c>
+      <c r="M24" s="47">
+        <v>0.51</v>
+      </c>
+      <c r="N24" s="45">
         <f>IF(ISBLANK(L24), "", L24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O24" s="45" t="str">
+        <v>18.75</v>
+      </c>
+      <c r="O24" s="45">
         <f>IF(ISBLANK(M24), "", M24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P24" s="44"/>
+        <v>12.75</v>
+      </c>
+      <c r="P24" s="44" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="41">
@@ -7657,30 +7996,48 @@
       </c>
       <c r="C25" s="42" t="str">
         <f>IF(ISBLANK(D25), "", _xlfn.CONCAT("T", TEXT(B25, "0000"), "/", VLOOKUP(D25, Internal!$B$35:C$39, 2, FALSE), IF(OR(D25="QA", D25="Revision"), _xlfn.CONCAT("/", H25), "")))</f>
-        <v/>
-      </c>
-      <c r="D25" s="44"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="44"/>
+        <v>T0015/D</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H25" s="43"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
+      <c r="I25" s="46">
+        <v>46139.444444444445</v>
+      </c>
+      <c r="J25" s="46">
+        <v>46139.520833333336</v>
+      </c>
       <c r="K25" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L25" s="47">
+        <v>0.33</v>
+      </c>
+      <c r="M25" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N25" s="45">
         <f>IF(ISBLANK(L25), "", L25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O25" s="45" t="str">
+        <v>8.25</v>
+      </c>
+      <c r="O25" s="45">
         <f>IF(ISBLANK(M25), "", M25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P25" s="44"/>
+        <v>6.25</v>
+      </c>
+      <c r="P25" s="44" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="41">
@@ -7688,30 +8045,48 @@
       </c>
       <c r="C26" s="42" t="str">
         <f>IF(ISBLANK(D26), "", _xlfn.CONCAT("T", TEXT(B26, "0000"), "/", VLOOKUP(D26, Internal!$B$35:C$39, 2, FALSE), IF(OR(D26="QA", D26="Revision"), _xlfn.CONCAT("/", H26), "")))</f>
-        <v/>
-      </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="44"/>
+        <v>T0016/D</v>
+      </c>
+      <c r="D26" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H26" s="43"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
+      <c r="I26" s="46">
+        <v>46139.444444444445</v>
+      </c>
+      <c r="J26" s="46">
+        <v>46139.75</v>
+      </c>
       <c r="K26" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L26" s="47">
+        <v>2</v>
+      </c>
+      <c r="M26" s="47">
+        <v>2.16</v>
+      </c>
+      <c r="N26" s="45">
         <f>IF(ISBLANK(L26), "", L26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O26" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O26" s="45">
         <f>IF(ISBLANK(M26), "", M26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P26" s="44"/>
+        <v>54</v>
+      </c>
+      <c r="P26" s="44" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="41">
@@ -7719,30 +8094,48 @@
       </c>
       <c r="C27" s="42" t="str">
         <f>IF(ISBLANK(D27), "", _xlfn.CONCAT("T", TEXT(B27, "0000"), "/", VLOOKUP(D27, Internal!$B$35:C$39, 2, FALSE), IF(OR(D27="QA", D27="Revision"), _xlfn.CONCAT("/", H27), "")))</f>
-        <v/>
-      </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="44"/>
+        <v>T0017/D</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H27" s="43"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
+      <c r="I27" s="46">
+        <v>46139.444444444445</v>
+      </c>
+      <c r="J27" s="46">
+        <v>46141.999305555553</v>
+      </c>
       <c r="K27" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L27" s="47">
+        <v>3</v>
+      </c>
+      <c r="M27" s="47">
+        <v>3.33</v>
+      </c>
+      <c r="N27" s="45">
         <f>IF(ISBLANK(L27), "", L27*VLOOKUP($F27,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O27" s="45" t="str">
+        <v>75</v>
+      </c>
+      <c r="O27" s="45">
         <f>IF(ISBLANK(M27), "", M27*VLOOKUP($F27,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P27" s="44"/>
+        <v>83.25</v>
+      </c>
+      <c r="P27" s="44" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="41">
@@ -7750,30 +8143,48 @@
       </c>
       <c r="C28" s="42" t="str">
         <f>IF(ISBLANK(D28), "", _xlfn.CONCAT("T", TEXT(B28, "0000"), "/", VLOOKUP(D28, Internal!$B$35:C$39, 2, FALSE), IF(OR(D28="QA", D28="Revision"), _xlfn.CONCAT("/", H28), "")))</f>
-        <v/>
-      </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="44"/>
+        <v>T0018/D</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H28" s="43"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
+      <c r="I28" s="46">
+        <v>46139.444444444445</v>
+      </c>
+      <c r="J28" s="46">
+        <v>46144.999305555553</v>
+      </c>
       <c r="K28" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L28" s="47">
+        <v>4.5</v>
+      </c>
+      <c r="M28" s="47">
+        <v>4</v>
+      </c>
+      <c r="N28" s="45">
         <f>IF(ISBLANK(L28), "", L28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O28" s="45" t="str">
+        <v>112.5</v>
+      </c>
+      <c r="O28" s="45">
         <f>IF(ISBLANK(M28), "", M28*VLOOKUP($F28,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P28" s="44"/>
+        <v>100</v>
+      </c>
+      <c r="P28" s="44" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="41">
@@ -7781,30 +8192,48 @@
       </c>
       <c r="C29" s="42" t="str">
         <f>IF(ISBLANK(D29), "", _xlfn.CONCAT("T", TEXT(B29, "0000"), "/", VLOOKUP(D29, Internal!$B$35:C$39, 2, FALSE), IF(OR(D29="QA", D29="Revision"), _xlfn.CONCAT("/", H29), "")))</f>
-        <v/>
-      </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="44"/>
+        <v>T0019/D</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H29" s="43"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
+      <c r="I29" s="46">
+        <v>46141</v>
+      </c>
+      <c r="J29" s="46">
+        <v>46141.999305555553</v>
+      </c>
       <c r="K29" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L29" s="47">
+        <v>0.83</v>
+      </c>
+      <c r="M29" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N29" s="45">
         <f>IF(ISBLANK(L29), "", L29*VLOOKUP($F29,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O29" s="45" t="str">
+        <v>20.75</v>
+      </c>
+      <c r="O29" s="45">
         <f>IF(ISBLANK(M29), "", M29*VLOOKUP($F29,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P29" s="44"/>
+        <v>6.25</v>
+      </c>
+      <c r="P29" s="44" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="41">
@@ -7812,30 +8241,48 @@
       </c>
       <c r="C30" s="42" t="str">
         <f>IF(ISBLANK(D30), "", _xlfn.CONCAT("T", TEXT(B30, "0000"), "/", VLOOKUP(D30, Internal!$B$35:C$39, 2, FALSE), IF(OR(D30="QA", D30="Revision"), _xlfn.CONCAT("/", H30), "")))</f>
-        <v/>
-      </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="44"/>
+        <v>T0020/D</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H30" s="43"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
+      <c r="I30" s="46">
+        <v>46141</v>
+      </c>
+      <c r="J30" s="46">
+        <v>46145.999305555553</v>
+      </c>
       <c r="K30" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L30" s="47">
+        <v>2</v>
+      </c>
+      <c r="M30" s="47">
+        <v>1.53</v>
+      </c>
+      <c r="N30" s="45">
         <f>IF(ISBLANK(L30), "", L30*VLOOKUP($F30,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O30" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O30" s="45">
         <f>IF(ISBLANK(M30), "", M30*VLOOKUP($F30,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P30" s="44"/>
+        <v>38.25</v>
+      </c>
+      <c r="P30" s="44" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="41">
@@ -7843,30 +8290,48 @@
       </c>
       <c r="C31" s="42" t="str">
         <f>IF(ISBLANK(D31), "", _xlfn.CONCAT("T", TEXT(B31, "0000"), "/", VLOOKUP(D31, Internal!$B$35:C$39, 2, FALSE), IF(OR(D31="QA", D31="Revision"), _xlfn.CONCAT("/", H31), "")))</f>
-        <v/>
-      </c>
-      <c r="D31" s="44"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44"/>
+        <v>T0021/D</v>
+      </c>
+      <c r="D31" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H31" s="43"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
+      <c r="I31" s="46">
+        <v>46143</v>
+      </c>
+      <c r="J31" s="46">
+        <v>46145.999305555553</v>
+      </c>
       <c r="K31" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L31" s="47"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L31" s="47">
+        <v>1</v>
+      </c>
+      <c r="M31" s="47">
+        <v>1</v>
+      </c>
+      <c r="N31" s="45">
         <f>IF(ISBLANK(L31), "", L31*VLOOKUP($F31,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O31" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O31" s="45">
         <f>IF(ISBLANK(M31), "", M31*VLOOKUP($F31,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P31" s="44"/>
+        <v>25</v>
+      </c>
+      <c r="P31" s="44" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="41">
@@ -7874,30 +8339,48 @@
       </c>
       <c r="C32" s="42" t="str">
         <f>IF(ISBLANK(D32), "", _xlfn.CONCAT("T", TEXT(B32, "0000"), "/", VLOOKUP(D32, Internal!$B$35:C$39, 2, FALSE), IF(OR(D32="QA", D32="Revision"), _xlfn.CONCAT("/", H32), "")))</f>
-        <v/>
-      </c>
-      <c r="D32" s="44"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="44"/>
+        <v>T0022/D</v>
+      </c>
+      <c r="D32" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H32" s="43"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
+      <c r="I32" s="46">
+        <v>46143</v>
+      </c>
+      <c r="J32" s="46">
+        <v>46145.999305555553</v>
+      </c>
       <c r="K32" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L32" s="47"/>
-      <c r="M32" s="47"/>
-      <c r="N32" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L32" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="M32" s="47">
+        <v>0.8</v>
+      </c>
+      <c r="N32" s="45">
         <f>IF(ISBLANK(L32), "", L32*VLOOKUP($F32,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O32" s="45" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="O32" s="45">
         <f>IF(ISBLANK(M32), "", M32*VLOOKUP($F32,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P32" s="44"/>
+        <v>20</v>
+      </c>
+      <c r="P32" s="44" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="41">
@@ -7905,30 +8388,48 @@
       </c>
       <c r="C33" s="42" t="str">
         <f>IF(ISBLANK(D33), "", _xlfn.CONCAT("T", TEXT(B33, "0000"), "/", VLOOKUP(D33, Internal!$B$35:C$39, 2, FALSE), IF(OR(D33="QA", D33="Revision"), _xlfn.CONCAT("/", H33), "")))</f>
-        <v/>
-      </c>
-      <c r="D33" s="44"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="44"/>
+        <v>T0023/D</v>
+      </c>
+      <c r="D33" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F33" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H33" s="43"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
+      <c r="I33" s="46">
+        <v>46143</v>
+      </c>
+      <c r="J33" s="46">
+        <v>46145</v>
+      </c>
       <c r="K33" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L33" s="47"/>
-      <c r="M33" s="47"/>
-      <c r="N33" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L33" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="M33" s="47">
+        <v>1.58</v>
+      </c>
+      <c r="N33" s="45">
         <f>IF(ISBLANK(L33), "", L33*VLOOKUP($F33,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O33" s="45" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="O33" s="45">
         <f>IF(ISBLANK(M33), "", M33*VLOOKUP($F33,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P33" s="44"/>
+        <v>39.5</v>
+      </c>
+      <c r="P33" s="44" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="41">
@@ -7936,30 +8437,48 @@
       </c>
       <c r="C34" s="42" t="str">
         <f>IF(ISBLANK(D34), "", _xlfn.CONCAT("T", TEXT(B34, "0000"), "/", VLOOKUP(D34, Internal!$B$35:C$39, 2, FALSE), IF(OR(D34="QA", D34="Revision"), _xlfn.CONCAT("/", H34), "")))</f>
-        <v/>
-      </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="44"/>
+        <v>T0024/D</v>
+      </c>
+      <c r="D34" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H34" s="43"/>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
+      <c r="I34" s="46">
+        <v>46141</v>
+      </c>
+      <c r="J34" s="46">
+        <v>46141.999305555553</v>
+      </c>
       <c r="K34" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L34" s="47">
+        <v>2</v>
+      </c>
+      <c r="M34" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="N34" s="45">
         <f>IF(ISBLANK(L34), "", L34*VLOOKUP($F34,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O34" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O34" s="45">
         <f>IF(ISBLANK(M34), "", M34*VLOOKUP($F34,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P34" s="44"/>
+        <v>45.75</v>
+      </c>
+      <c r="P34" s="44" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="41">
@@ -7967,30 +8486,48 @@
       </c>
       <c r="C35" s="42" t="str">
         <f>IF(ISBLANK(D35), "", _xlfn.CONCAT("T", TEXT(B35, "0000"), "/", VLOOKUP(D35, Internal!$B$35:C$39, 2, FALSE), IF(OR(D35="QA", D35="Revision"), _xlfn.CONCAT("/", H35), "")))</f>
-        <v/>
-      </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="44"/>
+        <v>T0025/D</v>
+      </c>
+      <c r="D35" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H35" s="43"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
+      <c r="I35" s="46">
+        <v>46142</v>
+      </c>
+      <c r="J35" s="46">
+        <v>46142.999305555553</v>
+      </c>
       <c r="K35" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L35" s="47">
+        <v>1</v>
+      </c>
+      <c r="M35" s="47">
+        <v>1.18</v>
+      </c>
+      <c r="N35" s="45">
         <f>IF(ISBLANK(L35), "", L35*VLOOKUP($F35,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O35" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O35" s="45">
         <f>IF(ISBLANK(M35), "", M35*VLOOKUP($F35,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P35" s="44"/>
+        <v>29.5</v>
+      </c>
+      <c r="P35" s="44" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="41">
@@ -7998,30 +8535,48 @@
       </c>
       <c r="C36" s="42" t="str">
         <f>IF(ISBLANK(D36), "", _xlfn.CONCAT("T", TEXT(B36, "0000"), "/", VLOOKUP(D36, Internal!$B$35:C$39, 2, FALSE), IF(OR(D36="QA", D36="Revision"), _xlfn.CONCAT("/", H36), "")))</f>
-        <v/>
-      </c>
-      <c r="D36" s="44"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="44"/>
+        <v>T0026/D</v>
+      </c>
+      <c r="D36" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H36" s="43"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
+      <c r="I36" s="46">
+        <v>46145</v>
+      </c>
+      <c r="J36" s="46">
+        <v>46145.999305555553</v>
+      </c>
       <c r="K36" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L36" s="47"/>
-      <c r="M36" s="47"/>
-      <c r="N36" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L36" s="47">
+        <v>4</v>
+      </c>
+      <c r="M36" s="47">
+        <v>5.38</v>
+      </c>
+      <c r="N36" s="45">
         <f>IF(ISBLANK(L36), "", L36*VLOOKUP($F36,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O36" s="45" t="str">
+        <v>100</v>
+      </c>
+      <c r="O36" s="45">
         <f>IF(ISBLANK(M36), "", M36*VLOOKUP($F36,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P36" s="44"/>
+        <v>134.5</v>
+      </c>
+      <c r="P36" s="44" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="41">
@@ -8029,30 +8584,48 @@
       </c>
       <c r="C37" s="42" t="str">
         <f>IF(ISBLANK(D37), "", _xlfn.CONCAT("T", TEXT(B37, "0000"), "/", VLOOKUP(D37, Internal!$B$35:C$39, 2, FALSE), IF(OR(D37="QA", D37="Revision"), _xlfn.CONCAT("/", H37), "")))</f>
-        <v/>
-      </c>
-      <c r="D37" s="44"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="44"/>
+        <v>T0027/D</v>
+      </c>
+      <c r="D37" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F37" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H37" s="43"/>
-      <c r="I37" s="46"/>
-      <c r="J37" s="46"/>
+      <c r="I37" s="46">
+        <v>46139.520833333336</v>
+      </c>
+      <c r="J37" s="46">
+        <v>46143.999305555553</v>
+      </c>
       <c r="K37" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L37" s="47"/>
-      <c r="M37" s="47"/>
-      <c r="N37" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L37" s="47">
+        <v>2</v>
+      </c>
+      <c r="M37" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="N37" s="45">
         <f>IF(ISBLANK(L37), "", L37*VLOOKUP($F37,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O37" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O37" s="45">
         <f>IF(ISBLANK(M37), "", M37*VLOOKUP($F37,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P37" s="44"/>
+        <v>45.75</v>
+      </c>
+      <c r="P37" s="44" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="41">
@@ -8060,30 +8633,48 @@
       </c>
       <c r="C38" s="42" t="str">
         <f>IF(ISBLANK(D38), "", _xlfn.CONCAT("T", TEXT(B38, "0000"), "/", VLOOKUP(D38, Internal!$B$35:C$39, 2, FALSE), IF(OR(D38="QA", D38="Revision"), _xlfn.CONCAT("/", H38), "")))</f>
-        <v/>
-      </c>
-      <c r="D38" s="44"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="44"/>
+        <v>T0028/D</v>
+      </c>
+      <c r="D38" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F38" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H38" s="43"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
+      <c r="I38" s="46">
+        <v>46143</v>
+      </c>
+      <c r="J38" s="46">
+        <v>46145.999305555553</v>
+      </c>
       <c r="K38" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L38" s="47"/>
-      <c r="M38" s="47"/>
-      <c r="N38" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L38" s="47">
+        <v>2</v>
+      </c>
+      <c r="M38" s="47">
+        <v>1.55</v>
+      </c>
+      <c r="N38" s="45">
         <f>IF(ISBLANK(L38), "", L38*VLOOKUP($F38,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O38" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O38" s="45">
         <f>IF(ISBLANK(M38), "", M38*VLOOKUP($F38,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P38" s="44"/>
+        <v>38.75</v>
+      </c>
+      <c r="P38" s="44" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="41">
@@ -8091,30 +8682,48 @@
       </c>
       <c r="C39" s="42" t="str">
         <f>IF(ISBLANK(D39), "", _xlfn.CONCAT("T", TEXT(B39, "0000"), "/", VLOOKUP(D39, Internal!$B$35:C$39, 2, FALSE), IF(OR(D39="QA", D39="Revision"), _xlfn.CONCAT("/", H39), "")))</f>
-        <v/>
-      </c>
-      <c r="D39" s="44"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="44"/>
+        <v>T0029/D</v>
+      </c>
+      <c r="D39" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F39" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H39" s="43"/>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
+      <c r="I39" s="46">
+        <v>46146</v>
+      </c>
+      <c r="J39" s="46">
+        <v>46146.999305555553</v>
+      </c>
       <c r="K39" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L39" s="47"/>
-      <c r="M39" s="47"/>
-      <c r="N39" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L39" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="M39" s="47">
+        <v>1.25</v>
+      </c>
+      <c r="N39" s="45">
         <f>IF(ISBLANK(L39), "", L39*VLOOKUP($F39,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O39" s="45" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="O39" s="45">
         <f>IF(ISBLANK(M39), "", M39*VLOOKUP($F39,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P39" s="44"/>
+        <v>31.25</v>
+      </c>
+      <c r="P39" s="44" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="41">
@@ -8122,30 +8731,48 @@
       </c>
       <c r="C40" s="42" t="str">
         <f>IF(ISBLANK(D40), "", _xlfn.CONCAT("T", TEXT(B40, "0000"), "/", VLOOKUP(D40, Internal!$B$35:C$39, 2, FALSE), IF(OR(D40="QA", D40="Revision"), _xlfn.CONCAT("/", H40), "")))</f>
-        <v/>
-      </c>
-      <c r="D40" s="44"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="44"/>
+        <v>T0030/D</v>
+      </c>
+      <c r="D40" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F40" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H40" s="43"/>
-      <c r="I40" s="46"/>
-      <c r="J40" s="46"/>
+      <c r="I40" s="46">
+        <v>46143</v>
+      </c>
+      <c r="J40" s="46">
+        <v>46143.999305555553</v>
+      </c>
       <c r="K40" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L40" s="47"/>
-      <c r="M40" s="47"/>
-      <c r="N40" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L40" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="M40" s="47">
+        <v>1.55</v>
+      </c>
+      <c r="N40" s="45">
         <f>IF(ISBLANK(L40), "", L40*VLOOKUP($F40,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O40" s="45" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="O40" s="45">
         <f>IF(ISBLANK(M40), "", M40*VLOOKUP($F40,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P40" s="44"/>
+        <v>38.75</v>
+      </c>
+      <c r="P40" s="44" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="41">
@@ -8153,30 +8780,48 @@
       </c>
       <c r="C41" s="42" t="str">
         <f>IF(ISBLANK(D41), "", _xlfn.CONCAT("T", TEXT(B41, "0000"), "/", VLOOKUP(D41, Internal!$B$35:C$39, 2, FALSE), IF(OR(D41="QA", D41="Revision"), _xlfn.CONCAT("/", H41), "")))</f>
-        <v/>
-      </c>
-      <c r="D41" s="44"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="44"/>
+        <v>T0031/D</v>
+      </c>
+      <c r="D41" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F41" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H41" s="43"/>
-      <c r="I41" s="46"/>
-      <c r="J41" s="46"/>
+      <c r="I41" s="46">
+        <v>46144</v>
+      </c>
+      <c r="J41" s="46">
+        <v>46144.999305555553</v>
+      </c>
       <c r="K41" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L41" s="47"/>
-      <c r="M41" s="47"/>
-      <c r="N41" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L41" s="47">
+        <v>2</v>
+      </c>
+      <c r="M41" s="47">
+        <v>2.5</v>
+      </c>
+      <c r="N41" s="45">
         <f>IF(ISBLANK(L41), "", L41*VLOOKUP($F41,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O41" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O41" s="45">
         <f>IF(ISBLANK(M41), "", M41*VLOOKUP($F41,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P41" s="44"/>
+        <v>62.5</v>
+      </c>
+      <c r="P41" s="44" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="41">
@@ -8184,30 +8829,48 @@
       </c>
       <c r="C42" s="42" t="str">
         <f>IF(ISBLANK(D42), "", _xlfn.CONCAT("T", TEXT(B42, "0000"), "/", VLOOKUP(D42, Internal!$B$35:C$39, 2, FALSE), IF(OR(D42="QA", D42="Revision"), _xlfn.CONCAT("/", H42), "")))</f>
-        <v/>
-      </c>
-      <c r="D42" s="44"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="44"/>
+        <v>T0032/D</v>
+      </c>
+      <c r="D42" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F42" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H42" s="43"/>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46"/>
+      <c r="I42" s="46">
+        <v>46146</v>
+      </c>
+      <c r="J42" s="46">
+        <v>46146.999305555553</v>
+      </c>
       <c r="K42" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L42" s="47"/>
-      <c r="M42" s="47"/>
-      <c r="N42" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L42" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="M42" s="47">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="N42" s="45">
         <f>IF(ISBLANK(L42), "", L42*VLOOKUP($F42,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O42" s="45" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="O42" s="45">
         <f>IF(ISBLANK(M42), "", M42*VLOOKUP($F42,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P42" s="44"/>
+        <v>28.749999999999996</v>
+      </c>
+      <c r="P42" s="44" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="41">
@@ -8215,12 +8878,20 @@
       </c>
       <c r="C43" s="42" t="str">
         <f>IF(ISBLANK(D43), "", _xlfn.CONCAT("T", TEXT(B43, "0000"), "/", VLOOKUP(D43, Internal!$B$35:C$39, 2, FALSE), IF(OR(D43="QA", D43="Revision"), _xlfn.CONCAT("/", H43), "")))</f>
-        <v/>
-      </c>
-      <c r="D43" s="44"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="44"/>
+        <v>T0033/D</v>
+      </c>
+      <c r="D43" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F43" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H43" s="43"/>
       <c r="I43" s="46"/>
       <c r="J43" s="46"/>

--- a/reports/Group/Planning-Template.xlsx
+++ b/reports/Group/Planning-Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPOSM\my\2C\dp2\workspace\Workspace-26\Projects\Acme-Starters-B\reports\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFC2F4F-3145-4B6B-A003-862E26C67CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EED8D2-4287-4AA2-88CA-949AA615390D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="281">
   <si>
     <t xml:space="preserve">  Enter configuration data in these cells</t>
   </si>
@@ -652,9 +652,6 @@
     <t>Publish project.</t>
   </si>
   <si>
-    <t>Implement list and show Inventios (Project-squad role).</t>
-  </si>
-  <si>
     <t>List member.</t>
   </si>
   <si>
@@ -680,6 +677,231 @@
   </si>
   <si>
     <t>List show auditReport , AuditSection</t>
+  </si>
+  <si>
+    <t>Add member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement list &amp; show components ,auditReports, sponosrships as Any role. </t>
+  </si>
+  <si>
+    <t>Components sample data</t>
+  </si>
+  <si>
+    <t>Test informally: obtain/update Manager role.</t>
+  </si>
+  <si>
+    <t>Test informally:  Create / list projects.</t>
+  </si>
+  <si>
+    <t>Test informally: Show and update a project.</t>
+  </si>
+  <si>
+    <t>T0015/D</t>
+  </si>
+  <si>
+    <t>Test informally: Implement Dashboard model.</t>
+  </si>
+  <si>
+    <t>T0016/D</t>
+  </si>
+  <si>
+    <t>Test informally: Implement Project , Managar , ProjectSquad, components model.</t>
+  </si>
+  <si>
+    <t>T0018/D</t>
+  </si>
+  <si>
+    <t>Test informally: Implement sponsorship, auditReport link with project, UI, model, service, controller.</t>
+  </si>
+  <si>
+    <t>Test informally: Implement list and show projects (Any role).</t>
+  </si>
+  <si>
+    <t>T0019/D</t>
+  </si>
+  <si>
+    <t>T0020/D</t>
+  </si>
+  <si>
+    <t>Test informally: Implement effort and TotalActiveMonths update  (update / publish / delete / assign in components).</t>
+  </si>
+  <si>
+    <t>Implement list and show Inventions (Project-squad role).</t>
+  </si>
+  <si>
+    <t>T0021/D</t>
+  </si>
+  <si>
+    <t>Test informally: Implement list and show Inventions (Project-squad role).</t>
+  </si>
+  <si>
+    <t>Test informally: Delete project.</t>
+  </si>
+  <si>
+    <t>Test informally: Publish project.</t>
+  </si>
+  <si>
+    <t>Test informally: List member.</t>
+  </si>
+  <si>
+    <t>T0025/D</t>
+  </si>
+  <si>
+    <t>Test informally: List member (Any role).</t>
+  </si>
+  <si>
+    <t>T0026/D</t>
+  </si>
+  <si>
+    <t>Test informally: Assign / unlink components.</t>
+  </si>
+  <si>
+    <t>T0027/D</t>
+  </si>
+  <si>
+    <t>Test informally: List spokespeople, fundrasisers, inventors thar aren't in the project.</t>
+  </si>
+  <si>
+    <t>T0028/D</t>
+  </si>
+  <si>
+    <t>Test informally: List show campaigns, strategies.</t>
+  </si>
+  <si>
+    <t>T0029/D</t>
+  </si>
+  <si>
+    <t>Test informally: List show sponsorship, donations.</t>
+  </si>
+  <si>
+    <t>T0030/D</t>
+  </si>
+  <si>
+    <t>Test informally: Implement Dashboard service and controller.</t>
+  </si>
+  <si>
+    <t>T0031/D</t>
+  </si>
+  <si>
+    <t>Test informally: Add Sample / Error data ( Project and Memeber ).</t>
+  </si>
+  <si>
+    <t>T0032/D</t>
+  </si>
+  <si>
+    <t>Test informally: List show auditReport , AuditSection</t>
+  </si>
+  <si>
+    <t>T0033/D</t>
+  </si>
+  <si>
+    <t>Test informally: Add member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test informally: Implement list &amp; show components ,auditReports, sponosrships as Any role. </t>
+  </si>
+  <si>
+    <t>Test infromally: Components sample data</t>
+  </si>
+  <si>
+    <t>Plan and organize the deliverable</t>
+  </si>
+  <si>
+    <t>Plan and organize missing parts of the deliverable</t>
+  </si>
+  <si>
+    <t>Plan and organize after problems with add member.</t>
+  </si>
+  <si>
+    <t>T0063/D</t>
+  </si>
+  <si>
+    <t>Add member with role Inventor.</t>
+  </si>
+  <si>
+    <t>Add member.</t>
+  </si>
+  <si>
+    <t>Test infromally: Add member with role Inventor.</t>
+  </si>
+  <si>
+    <t>Add member with role Spokesperson.</t>
+  </si>
+  <si>
+    <t>T0065/D</t>
+  </si>
+  <si>
+    <t>Test infromally: Add member with role Spokesperson.</t>
+  </si>
+  <si>
+    <t>Add member with role Fundraiser.</t>
+  </si>
+  <si>
+    <t>T0067/D</t>
+  </si>
+  <si>
+    <t>Test infromally: Add member with role Fundraiser.</t>
+  </si>
+  <si>
+    <t>Test formally: Add member with role Inventor.</t>
+  </si>
+  <si>
+    <t>Test formally: Create / list projects.</t>
+  </si>
+  <si>
+    <t>Test formally:   Implement Dashboard service and controller.</t>
+  </si>
+  <si>
+    <t>T0017/D</t>
+  </si>
+  <si>
+    <t>Test formally:   Implement banner model, service, controller, UI.</t>
+  </si>
+  <si>
+    <t>Finish Analysis report.</t>
+  </si>
+  <si>
+    <t>Write Lint report.</t>
+  </si>
+  <si>
+    <t>Implement indexs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test formally: Implement list &amp; show components ,auditReports, sponosrships as Any role. </t>
+  </si>
+  <si>
+    <t>Test formally: Publish project.</t>
+  </si>
+  <si>
+    <t>Test formally:  Implement list and show Inventions (Project-squad role).</t>
+  </si>
+  <si>
+    <t>Test formally: Show and update a project.</t>
+  </si>
+  <si>
+    <t>T0076/D</t>
+  </si>
+  <si>
+    <t>Test informally: Implement indexs.</t>
+  </si>
+  <si>
+    <t>Write test report.</t>
+  </si>
+  <si>
+    <t>Calculate Z-test  between test without and with indexs</t>
+  </si>
+  <si>
+    <t>Package deliverable.</t>
+  </si>
+  <si>
+    <t>Upload deliverable in EV.</t>
+  </si>
+  <si>
+    <t>T0085/D</t>
+  </si>
+  <si>
+    <t>Check deliverable.</t>
   </si>
 </sst>
 </file>
@@ -1069,17 +1291,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1091,7 +1313,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FFFFFF00"/>
@@ -1105,6 +1327,26 @@
     <dxf>
       <font>
         <strike val="0"/>
+        <color rgb="FFFFFF00"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFF00"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFFFF00"/>
       </font>
       <fill>
@@ -1725,20 +1967,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="57" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="60"/>
@@ -1854,17 +2096,17 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
@@ -1878,39 +2120,39 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
@@ -2010,40 +2252,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="59"/>
-      <c r="L4" s="59"/>
-      <c r="M4" s="59"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="59"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="5"/>
@@ -2062,7 +2304,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="58" t="s">
         <v>68</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -2085,7 +2327,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="56"/>
+      <c r="C7" s="58"/>
       <c r="D7" s="11" t="s">
         <v>70</v>
       </c>
@@ -2103,19 +2345,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="57"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="57" t="s">
+      <c r="L9" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57" t="s">
+      <c r="M9" s="59"/>
+      <c r="N9" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="O9" s="57"/>
+      <c r="O9" s="59"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7065,12 +7307,12 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="H11:H110">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J110">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7149,40 +7391,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="59"/>
-      <c r="L4" s="59"/>
-      <c r="M4" s="59"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="59"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="5"/>
@@ -7201,7 +7443,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="58" t="s">
         <v>68</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -7209,7 +7451,7 @@
       </c>
       <c r="E6" s="35">
         <f>SUM(N11:N110)</f>
-        <v>1157.75</v>
+        <v>2663.8100000000004</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -7224,13 +7466,13 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="56"/>
+      <c r="C7" s="58"/>
       <c r="D7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="E7" s="36">
         <f>SUM(O11:O110)</f>
-        <v>1146.5</v>
+        <v>2622.7300000000005</v>
       </c>
       <c r="J7" s="37"/>
     </row>
@@ -7242,19 +7484,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="57"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="57" t="s">
+      <c r="L9" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57" t="s">
+      <c r="M9" s="59"/>
+      <c r="N9" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="O9" s="57"/>
+      <c r="O9" s="59"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7381,7 +7623,7 @@
         <v>46121.430555555555</v>
       </c>
       <c r="K12" s="45" t="str">
-        <f t="shared" ref="K12:K75" ca="1" si="0">IF(OR(I12="",J12=""),"",IF(AND(J12&lt;&gt;"",I12&gt;=NOW()),"Planned",IF(AND(J12&lt;&gt;"",J12&lt;NOW()),"Completed","Ongoing")))</f>
+        <f ca="1">IF(OR(I12="",J12=""),"",IF(AND(J12&lt;&gt;"",I12&gt;=NOW()),"Planned",IF(AND(J12&lt;&gt;"",J12&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L12" s="47">
@@ -7430,7 +7672,7 @@
         <v>46125.520833333336</v>
       </c>
       <c r="K13" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I13="",J13=""),"",IF(AND(J13&lt;&gt;"",I13&gt;=NOW()),"Planned",IF(AND(J13&lt;&gt;"",J13&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L13" s="47">
@@ -7479,7 +7721,7 @@
         <v>46128.430555555555</v>
       </c>
       <c r="K14" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I14="",J14=""),"",IF(AND(J14&lt;&gt;"",I14&gt;=NOW()),"Planned",IF(AND(J14&lt;&gt;"",J14&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L14" s="47">
@@ -7528,7 +7770,7 @@
         <v>46139.520833333336</v>
       </c>
       <c r="K15" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I15="",J15=""),"",IF(AND(J15&lt;&gt;"",I15&gt;=NOW()),"Planned",IF(AND(J15&lt;&gt;"",J15&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L15" s="47">
@@ -7577,7 +7819,7 @@
         <v>46142.430555555555</v>
       </c>
       <c r="K16" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I16="",J16=""),"",IF(AND(J16&lt;&gt;"",I16&gt;=NOW()),"Planned",IF(AND(J16&lt;&gt;"",J16&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L16" s="47">
@@ -7626,7 +7868,7 @@
         <v>46146.520833333336</v>
       </c>
       <c r="K17" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I17="",J17=""),"",IF(AND(J17&lt;&gt;"",I17&gt;=NOW()),"Planned",IF(AND(J17&lt;&gt;"",J17&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L17" s="47">
@@ -7675,7 +7917,7 @@
         <v>46119.430555555555</v>
       </c>
       <c r="K18" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I18="",J18=""),"",IF(AND(J18&lt;&gt;"",I18&gt;=NOW()),"Planned",IF(AND(J18&lt;&gt;"",J18&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L18" s="47">
@@ -7724,7 +7966,7 @@
         <v>46124.999305555553</v>
       </c>
       <c r="K19" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I19="",J19=""),"",IF(AND(J19&lt;&gt;"",I19&gt;=NOW()),"Planned",IF(AND(J19&lt;&gt;"",J19&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L19" s="47">
@@ -7773,7 +8015,7 @@
         <v>46139.444444444445</v>
       </c>
       <c r="K20" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I20="",J20=""),"",IF(AND(J20&lt;&gt;"",I20&gt;=NOW()),"Planned",IF(AND(J20&lt;&gt;"",J20&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L20" s="47">
@@ -7822,7 +8064,7 @@
         <v>46139.999305555553</v>
       </c>
       <c r="K21" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I21="",J21=""),"",IF(AND(J21&lt;&gt;"",I21&gt;=NOW()),"Planned",IF(AND(J21&lt;&gt;"",J21&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L21" s="47">
@@ -7871,7 +8113,7 @@
         <v>46140.645833333336</v>
       </c>
       <c r="K22" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I22="",J22=""),"",IF(AND(J22&lt;&gt;"",I22&gt;=NOW()),"Planned",IF(AND(J22&lt;&gt;"",J22&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L22" s="47">
@@ -7920,7 +8162,7 @@
         <v>46140.999305555553</v>
       </c>
       <c r="K23" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I23="",J23=""),"",IF(AND(J23&lt;&gt;"",I23&gt;=NOW()),"Planned",IF(AND(J23&lt;&gt;"",J23&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L23" s="47">
@@ -7969,7 +8211,7 @@
         <v>46140.999305555553</v>
       </c>
       <c r="K24" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I24="",J24=""),"",IF(AND(J24&lt;&gt;"",I24&gt;=NOW()),"Planned",IF(AND(J24&lt;&gt;"",J24&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L24" s="47">
@@ -8018,7 +8260,7 @@
         <v>46139.520833333336</v>
       </c>
       <c r="K25" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I25="",J25=""),"",IF(AND(J25&lt;&gt;"",I25&gt;=NOW()),"Planned",IF(AND(J25&lt;&gt;"",J25&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L25" s="47">
@@ -8067,7 +8309,7 @@
         <v>46139.75</v>
       </c>
       <c r="K26" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I26="",J26=""),"",IF(AND(J26&lt;&gt;"",I26&gt;=NOW()),"Planned",IF(AND(J26&lt;&gt;"",J26&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L26" s="47">
@@ -8116,7 +8358,7 @@
         <v>46141.999305555553</v>
       </c>
       <c r="K27" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I27="",J27=""),"",IF(AND(J27&lt;&gt;"",I27&gt;=NOW()),"Planned",IF(AND(J27&lt;&gt;"",J27&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L27" s="47">
@@ -8165,7 +8407,7 @@
         <v>46144.999305555553</v>
       </c>
       <c r="K28" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I28="",J28=""),"",IF(AND(J28&lt;&gt;"",I28&gt;=NOW()),"Planned",IF(AND(J28&lt;&gt;"",J28&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L28" s="47">
@@ -8214,7 +8456,7 @@
         <v>46141.999305555553</v>
       </c>
       <c r="K29" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I29="",J29=""),"",IF(AND(J29&lt;&gt;"",I29&gt;=NOW()),"Planned",IF(AND(J29&lt;&gt;"",J29&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L29" s="47">
@@ -8260,10 +8502,10 @@
         <v>46141</v>
       </c>
       <c r="J30" s="46">
-        <v>46145.999305555553</v>
+        <v>46144.999305555553</v>
       </c>
       <c r="K30" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I30="",J30=""),"",IF(AND(J30&lt;&gt;"",I30&gt;=NOW()),"Planned",IF(AND(J30&lt;&gt;"",J30&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L30" s="47">
@@ -8309,10 +8551,10 @@
         <v>46143</v>
       </c>
       <c r="J31" s="46">
-        <v>46145.999305555553</v>
+        <v>46145.665972222225</v>
       </c>
       <c r="K31" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I31="",J31=""),"",IF(AND(J31&lt;&gt;"",I31&gt;=NOW()),"Planned",IF(AND(J31&lt;&gt;"",J31&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L31" s="47">
@@ -8330,7 +8572,7 @@
         <v>25</v>
       </c>
       <c r="P31" s="44" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8361,7 +8603,7 @@
         <v>46145.999305555553</v>
       </c>
       <c r="K32" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I32="",J32=""),"",IF(AND(J32&lt;&gt;"",I32&gt;=NOW()),"Planned",IF(AND(J32&lt;&gt;"",J32&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L32" s="47">
@@ -8407,10 +8649,10 @@
         <v>46143</v>
       </c>
       <c r="J33" s="46">
-        <v>46145</v>
+        <v>46145.999305555553</v>
       </c>
       <c r="K33" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I33="",J33=""),"",IF(AND(J33&lt;&gt;"",I33&gt;=NOW()),"Planned",IF(AND(J33&lt;&gt;"",J33&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L33" s="47">
@@ -8459,7 +8701,7 @@
         <v>46141.999305555553</v>
       </c>
       <c r="K34" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I34="",J34=""),"",IF(AND(J34&lt;&gt;"",I34&gt;=NOW()),"Planned",IF(AND(J34&lt;&gt;"",J34&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L34" s="47">
@@ -8477,7 +8719,7 @@
         <v>45.75</v>
       </c>
       <c r="P34" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8508,7 +8750,7 @@
         <v>46142.999305555553</v>
       </c>
       <c r="K35" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I35="",J35=""),"",IF(AND(J35&lt;&gt;"",I35&gt;=NOW()),"Planned",IF(AND(J35&lt;&gt;"",J35&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L35" s="47">
@@ -8526,7 +8768,7 @@
         <v>29.5</v>
       </c>
       <c r="P35" s="44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8554,10 +8796,10 @@
         <v>46145</v>
       </c>
       <c r="J36" s="46">
-        <v>46145.999305555553</v>
+        <v>46145.854166666664</v>
       </c>
       <c r="K36" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I36="",J36=""),"",IF(AND(J36&lt;&gt;"",I36&gt;=NOW()),"Planned",IF(AND(J36&lt;&gt;"",J36&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L36" s="47">
@@ -8575,7 +8817,7 @@
         <v>134.5</v>
       </c>
       <c r="P36" s="44" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8606,7 +8848,7 @@
         <v>46143.999305555553</v>
       </c>
       <c r="K37" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I37="",J37=""),"",IF(AND(J37&lt;&gt;"",I37&gt;=NOW()),"Planned",IF(AND(J37&lt;&gt;"",J37&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L37" s="47">
@@ -8624,7 +8866,7 @@
         <v>45.75</v>
       </c>
       <c r="P37" s="44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8652,10 +8894,10 @@
         <v>46143</v>
       </c>
       <c r="J38" s="46">
-        <v>46145.999305555553</v>
+        <v>46145.707638888889</v>
       </c>
       <c r="K38" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I38="",J38=""),"",IF(AND(J38&lt;&gt;"",I38&gt;=NOW()),"Planned",IF(AND(J38&lt;&gt;"",J38&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L38" s="47">
@@ -8673,7 +8915,7 @@
         <v>38.75</v>
       </c>
       <c r="P38" s="44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8701,10 +8943,10 @@
         <v>46146</v>
       </c>
       <c r="J39" s="46">
-        <v>46146.999305555553</v>
+        <v>46146.707638888889</v>
       </c>
       <c r="K39" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I39="",J39=""),"",IF(AND(J39&lt;&gt;"",I39&gt;=NOW()),"Planned",IF(AND(J39&lt;&gt;"",J39&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L39" s="47">
@@ -8722,7 +8964,7 @@
         <v>31.25</v>
       </c>
       <c r="P39" s="44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8753,7 +8995,7 @@
         <v>46143.999305555553</v>
       </c>
       <c r="K40" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I40="",J40=""),"",IF(AND(J40&lt;&gt;"",I40&gt;=NOW()),"Planned",IF(AND(J40&lt;&gt;"",J40&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L40" s="47">
@@ -8771,7 +9013,7 @@
         <v>38.75</v>
       </c>
       <c r="P40" s="44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8802,7 +9044,7 @@
         <v>46144.999305555553</v>
       </c>
       <c r="K41" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I41="",J41=""),"",IF(AND(J41&lt;&gt;"",I41&gt;=NOW()),"Planned",IF(AND(J41&lt;&gt;"",J41&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L41" s="47">
@@ -8820,7 +9062,7 @@
         <v>62.5</v>
       </c>
       <c r="P41" s="44" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8851,7 +9093,7 @@
         <v>46146.999305555553</v>
       </c>
       <c r="K42" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(OR(I42="",J42=""),"",IF(AND(J42&lt;&gt;"",I42&gt;=NOW()),"Planned",IF(AND(J42&lt;&gt;"",J42&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L42" s="47">
@@ -8869,7 +9111,7 @@
         <v>28.749999999999996</v>
       </c>
       <c r="P42" s="44" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8893,23 +9135,33 @@
         <v>41</v>
       </c>
       <c r="H43" s="43"/>
-      <c r="I43" s="46"/>
-      <c r="J43" s="46"/>
+      <c r="I43" s="46">
+        <v>46144</v>
+      </c>
+      <c r="J43" s="46">
+        <v>46145.853472222225</v>
+      </c>
       <c r="K43" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L43" s="47"/>
-      <c r="M43" s="47"/>
-      <c r="N43" s="45" t="str">
+        <f ca="1">IF(OR(I43="",J43=""),"",IF(AND(J43&lt;&gt;"",I43&gt;=NOW()),"Planned",IF(AND(J43&lt;&gt;"",J43&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L43" s="47">
+        <v>3.5</v>
+      </c>
+      <c r="M43" s="47">
+        <v>4</v>
+      </c>
+      <c r="N43" s="45">
         <f>IF(ISBLANK(L43), "", L43*VLOOKUP($F43,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O43" s="45" t="str">
+        <v>87.5</v>
+      </c>
+      <c r="O43" s="45">
         <f>IF(ISBLANK(M43), "", M43*VLOOKUP($F43,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P43" s="44"/>
+        <v>100</v>
+      </c>
+      <c r="P43" s="44" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="41">
@@ -8917,30 +9169,48 @@
       </c>
       <c r="C44" s="42" t="str">
         <f>IF(ISBLANK(D44), "", _xlfn.CONCAT("T", TEXT(B44, "0000"), "/", VLOOKUP(D44, Internal!$B$35:C$39, 2, FALSE), IF(OR(D44="QA", D44="Revision"), _xlfn.CONCAT("/", H44), "")))</f>
-        <v/>
-      </c>
-      <c r="D44" s="44"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="44"/>
+        <v>T0034/D</v>
+      </c>
+      <c r="D44" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F44" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H44" s="43"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
+      <c r="I44" s="46">
+        <v>46139.75</v>
+      </c>
+      <c r="J44" s="46">
+        <v>46145.665972222225</v>
+      </c>
       <c r="K44" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L44" s="47"/>
-      <c r="M44" s="47"/>
-      <c r="N44" s="45" t="str">
+        <f ca="1">IF(OR(I44="",J44=""),"",IF(AND(J44&lt;&gt;"",I44&gt;=NOW()),"Planned",IF(AND(J44&lt;&gt;"",J44&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L44" s="47">
+        <v>2</v>
+      </c>
+      <c r="M44" s="47">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="N44" s="45">
         <f>IF(ISBLANK(L44), "", L44*VLOOKUP($F44,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O44" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O44" s="45">
         <f>IF(ISBLANK(M44), "", M44*VLOOKUP($F44,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P44" s="44"/>
+        <v>55.000000000000007</v>
+      </c>
+      <c r="P44" s="44" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="41">
@@ -8948,30 +9218,48 @@
       </c>
       <c r="C45" s="42" t="str">
         <f>IF(ISBLANK(D45), "", _xlfn.CONCAT("T", TEXT(B45, "0000"), "/", VLOOKUP(D45, Internal!$B$35:C$39, 2, FALSE), IF(OR(D45="QA", D45="Revision"), _xlfn.CONCAT("/", H45), "")))</f>
-        <v/>
-      </c>
-      <c r="D45" s="44"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="44"/>
+        <v>T0035/D</v>
+      </c>
+      <c r="D45" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F45" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H45" s="43"/>
-      <c r="I45" s="46"/>
-      <c r="J45" s="46"/>
+      <c r="I45" s="46">
+        <v>46139.75</v>
+      </c>
+      <c r="J45" s="46">
+        <v>46142.999305555553</v>
+      </c>
       <c r="K45" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L45" s="47"/>
-      <c r="M45" s="47"/>
-      <c r="N45" s="45" t="str">
+        <f ca="1">IF(OR(I45="",J45=""),"",IF(AND(J45&lt;&gt;"",I45&gt;=NOW()),"Planned",IF(AND(J45&lt;&gt;"",J45&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L45" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="M45" s="47">
+        <v>1.25</v>
+      </c>
+      <c r="N45" s="45">
         <f>IF(ISBLANK(L45), "", L45*VLOOKUP($F45,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O45" s="45" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="O45" s="45">
         <f>IF(ISBLANK(M45), "", M45*VLOOKUP($F45,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P45" s="44"/>
+        <v>31.25</v>
+      </c>
+      <c r="P45" s="44" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B46" s="41">
@@ -8979,30 +9267,50 @@
       </c>
       <c r="C46" s="42" t="str">
         <f>IF(ISBLANK(D46), "", _xlfn.CONCAT("T", TEXT(B46, "0000"), "/", VLOOKUP(D46, Internal!$B$35:C$39, 2, FALSE), IF(OR(D46="QA", D46="Revision"), _xlfn.CONCAT("/", H46), "")))</f>
-        <v/>
-      </c>
-      <c r="D46" s="44"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="46"/>
-      <c r="J46" s="46"/>
+        <v>T0036/D</v>
+      </c>
+      <c r="D46" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F46" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H46" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="I46" s="46">
+        <v>46140</v>
+      </c>
+      <c r="J46" s="46">
+        <v>46140.999305555553</v>
+      </c>
       <c r="K46" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L46" s="47"/>
-      <c r="M46" s="47"/>
-      <c r="N46" s="45" t="str">
+        <f ca="1">IF(OR(I46="",J46=""),"",IF(AND(J46&lt;&gt;"",I46&gt;=NOW()),"Planned",IF(AND(J46&lt;&gt;"",J46&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L46" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M46" s="47">
+        <v>0.33</v>
+      </c>
+      <c r="N46" s="45">
         <f>IF(ISBLANK(L46), "", L46*VLOOKUP($F46,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O46" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O46" s="45">
         <f>IF(ISBLANK(M46), "", M46*VLOOKUP($F46,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P46" s="44"/>
+        <v>8.25</v>
+      </c>
+      <c r="P46" s="44" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="41">
@@ -9010,30 +9318,50 @@
       </c>
       <c r="C47" s="42" t="str">
         <f>IF(ISBLANK(D47), "", _xlfn.CONCAT("T", TEXT(B47, "0000"), "/", VLOOKUP(D47, Internal!$B$35:C$39, 2, FALSE), IF(OR(D47="QA", D47="Revision"), _xlfn.CONCAT("/", H47), "")))</f>
-        <v/>
-      </c>
-      <c r="D47" s="44"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="43"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="46"/>
+        <v>T0037/D</v>
+      </c>
+      <c r="D47" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F47" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H47" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="I47" s="46">
+        <v>46140.645833333336</v>
+      </c>
+      <c r="J47" s="46">
+        <v>46140.999305555553</v>
+      </c>
       <c r="K47" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L47" s="47"/>
-      <c r="M47" s="47"/>
-      <c r="N47" s="45" t="str">
+        <f ca="1">IF(OR(I47="",J47=""),"",IF(AND(J47&lt;&gt;"",I47&gt;=NOW()),"Planned",IF(AND(J47&lt;&gt;"",J47&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L47" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M47" s="47">
+        <v>0.38</v>
+      </c>
+      <c r="N47" s="45">
         <f>IF(ISBLANK(L47), "", L47*VLOOKUP($F47,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O47" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O47" s="45">
         <f>IF(ISBLANK(M47), "", M47*VLOOKUP($F47,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P47" s="44"/>
+        <v>9.5</v>
+      </c>
+      <c r="P47" s="44" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="41">
@@ -9041,30 +9369,50 @@
       </c>
       <c r="C48" s="42" t="str">
         <f>IF(ISBLANK(D48), "", _xlfn.CONCAT("T", TEXT(B48, "0000"), "/", VLOOKUP(D48, Internal!$B$35:C$39, 2, FALSE), IF(OR(D48="QA", D48="Revision"), _xlfn.CONCAT("/", H48), "")))</f>
-        <v/>
-      </c>
-      <c r="D48" s="44"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="44"/>
-      <c r="H48" s="43"/>
-      <c r="I48" s="46"/>
-      <c r="J48" s="46"/>
+        <v>T0038/D</v>
+      </c>
+      <c r="D48" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F48" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H48" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="I48" s="46">
+        <v>46141</v>
+      </c>
+      <c r="J48" s="46">
+        <v>46141.999305555553</v>
+      </c>
       <c r="K48" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L48" s="47"/>
-      <c r="M48" s="47"/>
-      <c r="N48" s="45" t="str">
+        <f ca="1">IF(OR(I48="",J48=""),"",IF(AND(J48&lt;&gt;"",I48&gt;=NOW()),"Planned",IF(AND(J48&lt;&gt;"",J48&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L48" s="47">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="M48" s="47">
+        <v>0.33</v>
+      </c>
+      <c r="N48" s="45">
         <f>IF(ISBLANK(L48), "", L48*VLOOKUP($F48,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O48" s="45" t="str">
+        <v>10.4</v>
+      </c>
+      <c r="O48" s="45">
         <f>IF(ISBLANK(M48), "", M48*VLOOKUP($F48,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P48" s="44"/>
+        <v>8.25</v>
+      </c>
+      <c r="P48" s="44" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B49" s="41">
@@ -9072,30 +9420,50 @@
       </c>
       <c r="C49" s="42" t="str">
         <f>IF(ISBLANK(D49), "", _xlfn.CONCAT("T", TEXT(B49, "0000"), "/", VLOOKUP(D49, Internal!$B$35:C$39, 2, FALSE), IF(OR(D49="QA", D49="Revision"), _xlfn.CONCAT("/", H49), "")))</f>
-        <v/>
-      </c>
-      <c r="D49" s="44"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="44"/>
-      <c r="H49" s="43"/>
-      <c r="I49" s="46"/>
-      <c r="J49" s="46"/>
+        <v>T0039/D</v>
+      </c>
+      <c r="D49" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F49" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H49" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="I49" s="46">
+        <v>46139.520833333336</v>
+      </c>
+      <c r="J49" s="46">
+        <v>46142.999305555553</v>
+      </c>
       <c r="K49" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L49" s="47"/>
-      <c r="M49" s="47"/>
-      <c r="N49" s="45" t="str">
+        <f ca="1">IF(OR(I49="",J49=""),"",IF(AND(J49&lt;&gt;"",I49&gt;=NOW()),"Planned",IF(AND(J49&lt;&gt;"",J49&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L49" s="47">
+        <v>0.16</v>
+      </c>
+      <c r="M49" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N49" s="45">
         <f>IF(ISBLANK(L49), "", L49*VLOOKUP($F49,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O49" s="45" t="str">
+        <v>4</v>
+      </c>
+      <c r="O49" s="45">
         <f>IF(ISBLANK(M49), "", M49*VLOOKUP($F49,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P49" s="44"/>
+        <v>6.25</v>
+      </c>
+      <c r="P49" s="44" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B50" s="41">
@@ -9103,30 +9471,50 @@
       </c>
       <c r="C50" s="42" t="str">
         <f>IF(ISBLANK(D50), "", _xlfn.CONCAT("T", TEXT(B50, "0000"), "/", VLOOKUP(D50, Internal!$B$35:C$39, 2, FALSE), IF(OR(D50="QA", D50="Revision"), _xlfn.CONCAT("/", H50), "")))</f>
-        <v/>
-      </c>
-      <c r="D50" s="44"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="43"/>
-      <c r="I50" s="46"/>
-      <c r="J50" s="46"/>
+        <v>T0040/D</v>
+      </c>
+      <c r="D50" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F50" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H50" s="43" t="s">
+        <v>214</v>
+      </c>
+      <c r="I50" s="46">
+        <v>46139.75</v>
+      </c>
+      <c r="J50" s="46">
+        <v>46139.999305555553</v>
+      </c>
       <c r="K50" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L50" s="47"/>
-      <c r="M50" s="47"/>
-      <c r="N50" s="45" t="str">
+        <f ca="1">IF(OR(I50="",J50=""),"",IF(AND(J50&lt;&gt;"",I50&gt;=NOW()),"Planned",IF(AND(J50&lt;&gt;"",J50&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L50" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M50" s="47">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="N50" s="45">
         <f>IF(ISBLANK(L50), "", L50*VLOOKUP($F50,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O50" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O50" s="45">
         <f>IF(ISBLANK(M50), "", M50*VLOOKUP($F50,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P50" s="44"/>
+        <v>14.499999999999998</v>
+      </c>
+      <c r="P50" s="44" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B51" s="41">
@@ -9134,30 +9522,50 @@
       </c>
       <c r="C51" s="42" t="str">
         <f>IF(ISBLANK(D51), "", _xlfn.CONCAT("T", TEXT(B51, "0000"), "/", VLOOKUP(D51, Internal!$B$35:C$39, 2, FALSE), IF(OR(D51="QA", D51="Revision"), _xlfn.CONCAT("/", H51), "")))</f>
-        <v/>
-      </c>
-      <c r="D51" s="44"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="44"/>
-      <c r="H51" s="43"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
+        <v>T0041/D</v>
+      </c>
+      <c r="D51" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E51" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F51" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G51" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H51" s="43" t="s">
+        <v>216</v>
+      </c>
+      <c r="I51" s="46">
+        <v>46145</v>
+      </c>
+      <c r="J51" s="46">
+        <v>46145.999305555553</v>
+      </c>
       <c r="K51" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L51" s="47"/>
-      <c r="M51" s="47"/>
-      <c r="N51" s="45" t="str">
+        <f ca="1">IF(OR(I51="",J51=""),"",IF(AND(J51&lt;&gt;"",I51&gt;=NOW()),"Planned",IF(AND(J51&lt;&gt;"",J51&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L51" s="47">
+        <v>1</v>
+      </c>
+      <c r="M51" s="47">
+        <v>0.66</v>
+      </c>
+      <c r="N51" s="45">
         <f>IF(ISBLANK(L51), "", L51*VLOOKUP($F51,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O51" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O51" s="45">
         <f>IF(ISBLANK(M51), "", M51*VLOOKUP($F51,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P51" s="44"/>
+        <v>16.5</v>
+      </c>
+      <c r="P51" s="44" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="41">
@@ -9165,30 +9573,50 @@
       </c>
       <c r="C52" s="42" t="str">
         <f>IF(ISBLANK(D52), "", _xlfn.CONCAT("T", TEXT(B52, "0000"), "/", VLOOKUP(D52, Internal!$B$35:C$39, 2, FALSE), IF(OR(D52="QA", D52="Revision"), _xlfn.CONCAT("/", H52), "")))</f>
-        <v/>
-      </c>
-      <c r="D52" s="44"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="43"/>
-      <c r="G52" s="44"/>
-      <c r="H52" s="43"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
+        <v>T0042/D</v>
+      </c>
+      <c r="D52" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F52" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G52" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H52" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="I52" s="46">
+        <v>46142</v>
+      </c>
+      <c r="J52" s="46">
+        <v>46142.999305555553</v>
+      </c>
       <c r="K52" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L52" s="47"/>
-      <c r="M52" s="47"/>
-      <c r="N52" s="45" t="str">
+        <f ca="1">IF(OR(I52="",J52=""),"",IF(AND(J52&lt;&gt;"",I52&gt;=NOW()),"Planned",IF(AND(J52&lt;&gt;"",J52&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L52" s="47">
+        <v>0.33</v>
+      </c>
+      <c r="M52" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N52" s="45">
         <f>IF(ISBLANK(L52), "", L52*VLOOKUP($F52,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O52" s="45" t="str">
+        <v>8.25</v>
+      </c>
+      <c r="O52" s="45">
         <f>IF(ISBLANK(M52), "", M52*VLOOKUP($F52,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P52" s="44"/>
+        <v>6.25</v>
+      </c>
+      <c r="P52" s="44" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="41">
@@ -9196,30 +9624,50 @@
       </c>
       <c r="C53" s="42" t="str">
         <f>IF(ISBLANK(D53), "", _xlfn.CONCAT("T", TEXT(B53, "0000"), "/", VLOOKUP(D53, Internal!$B$35:C$39, 2, FALSE), IF(OR(D53="QA", D53="Revision"), _xlfn.CONCAT("/", H53), "")))</f>
-        <v/>
-      </c>
-      <c r="D53" s="44"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="43"/>
-      <c r="G53" s="44"/>
-      <c r="H53" s="43"/>
-      <c r="I53" s="46"/>
-      <c r="J53" s="46"/>
+        <v>T0043/D</v>
+      </c>
+      <c r="D53" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F53" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H53" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="I53" s="46">
+        <v>46145</v>
+      </c>
+      <c r="J53" s="46">
+        <v>46145.999305555553</v>
+      </c>
       <c r="K53" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L53" s="47"/>
-      <c r="M53" s="47"/>
-      <c r="N53" s="45" t="str">
+        <f ca="1">IF(OR(I53="",J53=""),"",IF(AND(J53&lt;&gt;"",I53&gt;=NOW()),"Planned",IF(AND(J53&lt;&gt;"",J53&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L53" s="47">
+        <v>0.33</v>
+      </c>
+      <c r="M53" s="47">
+        <v>0.2</v>
+      </c>
+      <c r="N53" s="45">
         <f>IF(ISBLANK(L53), "", L53*VLOOKUP($F53,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O53" s="45" t="str">
+        <v>8.25</v>
+      </c>
+      <c r="O53" s="45">
         <f>IF(ISBLANK(M53), "", M53*VLOOKUP($F53,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P53" s="44"/>
+        <v>5</v>
+      </c>
+      <c r="P53" s="44" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="41">
@@ -9227,30 +9675,50 @@
       </c>
       <c r="C54" s="42" t="str">
         <f>IF(ISBLANK(D54), "", _xlfn.CONCAT("T", TEXT(B54, "0000"), "/", VLOOKUP(D54, Internal!$B$35:C$39, 2, FALSE), IF(OR(D54="QA", D54="Revision"), _xlfn.CONCAT("/", H54), "")))</f>
-        <v/>
-      </c>
-      <c r="D54" s="44"/>
-      <c r="E54" s="43"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="44"/>
-      <c r="H54" s="43"/>
-      <c r="I54" s="46"/>
-      <c r="J54" s="46"/>
+        <v>T0044/D</v>
+      </c>
+      <c r="D54" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F54" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G54" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H54" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="I54" s="46">
+        <v>46145.665972222225</v>
+      </c>
+      <c r="J54" s="46">
+        <v>46145.999305555553</v>
+      </c>
       <c r="K54" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L54" s="47"/>
-      <c r="M54" s="47"/>
-      <c r="N54" s="45" t="str">
+        <f ca="1">IF(OR(I54="",J54=""),"",IF(AND(J54&lt;&gt;"",I54&gt;=NOW()),"Planned",IF(AND(J54&lt;&gt;"",J54&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L54" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M54" s="47">
+        <v>0.36</v>
+      </c>
+      <c r="N54" s="45">
         <f>IF(ISBLANK(L54), "", L54*VLOOKUP($F54,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O54" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O54" s="45">
         <f>IF(ISBLANK(M54), "", M54*VLOOKUP($F54,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P54" s="44"/>
+        <v>9</v>
+      </c>
+      <c r="P54" s="44" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="41">
@@ -9258,30 +9726,50 @@
       </c>
       <c r="C55" s="42" t="str">
         <f>IF(ISBLANK(D55), "", _xlfn.CONCAT("T", TEXT(B55, "0000"), "/", VLOOKUP(D55, Internal!$B$35:C$39, 2, FALSE), IF(OR(D55="QA", D55="Revision"), _xlfn.CONCAT("/", H55), "")))</f>
-        <v/>
-      </c>
-      <c r="D55" s="44"/>
-      <c r="E55" s="43"/>
-      <c r="F55" s="43"/>
-      <c r="G55" s="44"/>
-      <c r="H55" s="43"/>
-      <c r="I55" s="46"/>
-      <c r="J55" s="46"/>
+        <v>T0045/D</v>
+      </c>
+      <c r="D55" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F55" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G55" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H55" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="I55" s="46">
+        <v>46146</v>
+      </c>
+      <c r="J55" s="46">
+        <v>46146.520833333336</v>
+      </c>
       <c r="K55" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L55" s="47"/>
-      <c r="M55" s="47"/>
-      <c r="N55" s="45" t="str">
+        <f ca="1">IF(OR(I55="",J55=""),"",IF(AND(J55&lt;&gt;"",I55&gt;=NOW()),"Planned",IF(AND(J55&lt;&gt;"",J55&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L55" s="47">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="M55" s="47">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N55" s="45">
         <f>IF(ISBLANK(L55), "", L55*VLOOKUP($F55,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O55" s="45" t="str">
+        <v>10.4</v>
+      </c>
+      <c r="O55" s="45">
         <f>IF(ISBLANK(M55), "", M55*VLOOKUP($F55,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P55" s="44"/>
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="P55" s="44" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="41">
@@ -9289,30 +9777,50 @@
       </c>
       <c r="C56" s="42" t="str">
         <f>IF(ISBLANK(D56), "", _xlfn.CONCAT("T", TEXT(B56, "0000"), "/", VLOOKUP(D56, Internal!$B$35:C$39, 2, FALSE), IF(OR(D56="QA", D56="Revision"), _xlfn.CONCAT("/", H56), "")))</f>
-        <v/>
-      </c>
-      <c r="D56" s="44"/>
-      <c r="E56" s="43"/>
-      <c r="F56" s="43"/>
-      <c r="G56" s="44"/>
-      <c r="H56" s="43"/>
-      <c r="I56" s="46"/>
-      <c r="J56" s="46"/>
+        <v>T0046/D</v>
+      </c>
+      <c r="D56" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E56" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F56" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G56" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H56" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="I56" s="46">
+        <v>46146</v>
+      </c>
+      <c r="J56" s="46">
+        <v>46146.520833333336</v>
+      </c>
       <c r="K56" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L56" s="47"/>
-      <c r="M56" s="47"/>
-      <c r="N56" s="45" t="str">
+        <f ca="1">IF(OR(I56="",J56=""),"",IF(AND(J56&lt;&gt;"",I56&gt;=NOW()),"Planned",IF(AND(J56&lt;&gt;"",J56&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L56" s="47">
+        <v>0.42</v>
+      </c>
+      <c r="M56" s="47">
+        <v>0.3</v>
+      </c>
+      <c r="N56" s="45">
         <f>IF(ISBLANK(L56), "", L56*VLOOKUP($F56,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O56" s="45" t="str">
+        <v>10.5</v>
+      </c>
+      <c r="O56" s="45">
         <f>IF(ISBLANK(M56), "", M56*VLOOKUP($F56,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P56" s="44"/>
+        <v>7.5</v>
+      </c>
+      <c r="P56" s="44" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="41">
@@ -9320,30 +9828,50 @@
       </c>
       <c r="C57" s="42" t="str">
         <f>IF(ISBLANK(D57), "", _xlfn.CONCAT("T", TEXT(B57, "0000"), "/", VLOOKUP(D57, Internal!$B$35:C$39, 2, FALSE), IF(OR(D57="QA", D57="Revision"), _xlfn.CONCAT("/", H57), "")))</f>
-        <v/>
-      </c>
-      <c r="D57" s="44"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="44"/>
-      <c r="H57" s="43"/>
-      <c r="I57" s="46"/>
-      <c r="J57" s="46"/>
+        <v>T0047/D</v>
+      </c>
+      <c r="D57" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E57" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F57" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G57" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H57" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="I57" s="46">
+        <v>46142</v>
+      </c>
+      <c r="J57" s="46">
+        <v>46142.999305555553</v>
+      </c>
       <c r="K57" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L57" s="47"/>
-      <c r="M57" s="47"/>
-      <c r="N57" s="45" t="str">
+        <f ca="1">IF(OR(I57="",J57=""),"",IF(AND(J57&lt;&gt;"",I57&gt;=NOW()),"Planned",IF(AND(J57&lt;&gt;"",J57&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L57" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M57" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N57" s="45">
         <f>IF(ISBLANK(L57), "", L57*VLOOKUP($F57,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O57" s="45" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="O57" s="45">
         <f>IF(ISBLANK(M57), "", M57*VLOOKUP($F57,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P57" s="44"/>
+        <v>6.25</v>
+      </c>
+      <c r="P57" s="44" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="41">
@@ -9351,30 +9879,50 @@
       </c>
       <c r="C58" s="42" t="str">
         <f>IF(ISBLANK(D58), "", _xlfn.CONCAT("T", TEXT(B58, "0000"), "/", VLOOKUP(D58, Internal!$B$35:C$39, 2, FALSE), IF(OR(D58="QA", D58="Revision"), _xlfn.CONCAT("/", H58), "")))</f>
-        <v/>
-      </c>
-      <c r="D58" s="44"/>
-      <c r="E58" s="43"/>
-      <c r="F58" s="43"/>
-      <c r="G58" s="44"/>
-      <c r="H58" s="43"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="46"/>
+        <v>T0048/D</v>
+      </c>
+      <c r="D58" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E58" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F58" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G58" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H58" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="I58" s="46">
+        <v>46142</v>
+      </c>
+      <c r="J58" s="46">
+        <v>46142.999305555553</v>
+      </c>
       <c r="K58" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L58" s="47"/>
-      <c r="M58" s="47"/>
-      <c r="N58" s="45" t="str">
+        <f ca="1">IF(OR(I58="",J58=""),"",IF(AND(J58&lt;&gt;"",I58&gt;=NOW()),"Planned",IF(AND(J58&lt;&gt;"",J58&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L58" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M58" s="47">
+        <v>0.11</v>
+      </c>
+      <c r="N58" s="45">
         <f>IF(ISBLANK(L58), "", L58*VLOOKUP($F58,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O58" s="45" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="O58" s="45">
         <f>IF(ISBLANK(M58), "", M58*VLOOKUP($F58,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P58" s="44"/>
+        <v>2.75</v>
+      </c>
+      <c r="P58" s="44" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B59" s="41">
@@ -9382,30 +9930,50 @@
       </c>
       <c r="C59" s="42" t="str">
         <f>IF(ISBLANK(D59), "", _xlfn.CONCAT("T", TEXT(B59, "0000"), "/", VLOOKUP(D59, Internal!$B$35:C$39, 2, FALSE), IF(OR(D59="QA", D59="Revision"), _xlfn.CONCAT("/", H59), "")))</f>
-        <v/>
-      </c>
-      <c r="D59" s="44"/>
-      <c r="E59" s="43"/>
-      <c r="F59" s="43"/>
-      <c r="G59" s="44"/>
-      <c r="H59" s="43"/>
-      <c r="I59" s="46"/>
-      <c r="J59" s="46"/>
+        <v>T0049/D</v>
+      </c>
+      <c r="D59" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E59" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F59" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G59" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H59" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="I59" s="46">
+        <v>46145.854166666664</v>
+      </c>
+      <c r="J59" s="46">
+        <v>46146.444444444445</v>
+      </c>
       <c r="K59" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L59" s="47"/>
-      <c r="M59" s="47"/>
-      <c r="N59" s="45" t="str">
+        <f ca="1">IF(OR(I59="",J59=""),"",IF(AND(J59&lt;&gt;"",I59&gt;=NOW()),"Planned",IF(AND(J59&lt;&gt;"",J59&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L59" s="47">
+        <v>0.75</v>
+      </c>
+      <c r="M59" s="47">
+        <v>0.7</v>
+      </c>
+      <c r="N59" s="45">
         <f>IF(ISBLANK(L59), "", L59*VLOOKUP($F59,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O59" s="45" t="str">
+        <v>18.75</v>
+      </c>
+      <c r="O59" s="45">
         <f>IF(ISBLANK(M59), "", M59*VLOOKUP($F59,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P59" s="44"/>
+        <v>17.5</v>
+      </c>
+      <c r="P59" s="44" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B60" s="41">
@@ -9413,30 +9981,50 @@
       </c>
       <c r="C60" s="42" t="str">
         <f>IF(ISBLANK(D60), "", _xlfn.CONCAT("T", TEXT(B60, "0000"), "/", VLOOKUP(D60, Internal!$B$35:C$39, 2, FALSE), IF(OR(D60="QA", D60="Revision"), _xlfn.CONCAT("/", H60), "")))</f>
-        <v/>
-      </c>
-      <c r="D60" s="44"/>
-      <c r="E60" s="43"/>
-      <c r="F60" s="43"/>
-      <c r="G60" s="44"/>
-      <c r="H60" s="43"/>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
+        <v>T0050/D</v>
+      </c>
+      <c r="D60" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E60" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F60" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G60" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H60" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="I60" s="46">
+        <v>46144</v>
+      </c>
+      <c r="J60" s="46">
+        <v>46144.999305555553</v>
+      </c>
       <c r="K60" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L60" s="47"/>
-      <c r="M60" s="47"/>
-      <c r="N60" s="45" t="str">
+        <f ca="1">IF(OR(I60="",J60=""),"",IF(AND(J60&lt;&gt;"",I60&gt;=NOW()),"Planned",IF(AND(J60&lt;&gt;"",J60&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L60" s="47">
+        <v>0.42</v>
+      </c>
+      <c r="M60" s="47">
+        <v>0.216</v>
+      </c>
+      <c r="N60" s="45">
         <f>IF(ISBLANK(L60), "", L60*VLOOKUP($F60,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O60" s="45" t="str">
+        <v>10.5</v>
+      </c>
+      <c r="O60" s="45">
         <f>IF(ISBLANK(M60), "", M60*VLOOKUP($F60,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P60" s="44"/>
+        <v>5.4</v>
+      </c>
+      <c r="P60" s="44" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="41">
@@ -9444,30 +10032,50 @@
       </c>
       <c r="C61" s="42" t="str">
         <f>IF(ISBLANK(D61), "", _xlfn.CONCAT("T", TEXT(B61, "0000"), "/", VLOOKUP(D61, Internal!$B$35:C$39, 2, FALSE), IF(OR(D61="QA", D61="Revision"), _xlfn.CONCAT("/", H61), "")))</f>
-        <v/>
-      </c>
-      <c r="D61" s="44"/>
-      <c r="E61" s="43"/>
-      <c r="F61" s="43"/>
-      <c r="G61" s="44"/>
-      <c r="H61" s="43"/>
-      <c r="I61" s="46"/>
-      <c r="J61" s="46"/>
+        <v>T0051/D</v>
+      </c>
+      <c r="D61" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E61" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F61" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G61" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H61" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="I61" s="46">
+        <v>46145.708333333336</v>
+      </c>
+      <c r="J61" s="46">
+        <v>46145.999305555553</v>
+      </c>
       <c r="K61" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L61" s="47"/>
-      <c r="M61" s="47"/>
-      <c r="N61" s="45" t="str">
+        <f ca="1">IF(OR(I61="",J61=""),"",IF(AND(J61&lt;&gt;"",I61&gt;=NOW()),"Planned",IF(AND(J61&lt;&gt;"",J61&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L61" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M61" s="47">
+        <v>0.3</v>
+      </c>
+      <c r="N61" s="45">
         <f>IF(ISBLANK(L61), "", L61*VLOOKUP($F61,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O61" s="45" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="O61" s="45">
         <f>IF(ISBLANK(M61), "", M61*VLOOKUP($F61,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P61" s="44"/>
+        <v>7.5</v>
+      </c>
+      <c r="P61" s="44" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="41">
@@ -9475,30 +10083,50 @@
       </c>
       <c r="C62" s="42" t="str">
         <f>IF(ISBLANK(D62), "", _xlfn.CONCAT("T", TEXT(B62, "0000"), "/", VLOOKUP(D62, Internal!$B$35:C$39, 2, FALSE), IF(OR(D62="QA", D62="Revision"), _xlfn.CONCAT("/", H62), "")))</f>
-        <v/>
-      </c>
-      <c r="D62" s="44"/>
-      <c r="E62" s="43"/>
-      <c r="F62" s="43"/>
-      <c r="G62" s="44"/>
-      <c r="H62" s="43"/>
-      <c r="I62" s="46"/>
-      <c r="J62" s="46"/>
+        <v>T0052/D</v>
+      </c>
+      <c r="D62" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E62" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F62" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G62" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H62" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="I62" s="46">
+        <v>46145.708333333336</v>
+      </c>
+      <c r="J62" s="46">
+        <v>46145.999305555553</v>
+      </c>
       <c r="K62" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L62" s="47"/>
-      <c r="M62" s="47"/>
-      <c r="N62" s="45" t="str">
+        <f ca="1">IF(OR(I62="",J62=""),"",IF(AND(J62&lt;&gt;"",I62&gt;=NOW()),"Planned",IF(AND(J62&lt;&gt;"",J62&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L62" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M62" s="47">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="N62" s="45">
         <f>IF(ISBLANK(L62), "", L62*VLOOKUP($F62,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O62" s="45" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="O62" s="45">
         <f>IF(ISBLANK(M62), "", M62*VLOOKUP($F62,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P62" s="44"/>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="P62" s="44" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B63" s="41">
@@ -9506,30 +10134,50 @@
       </c>
       <c r="C63" s="42" t="str">
         <f>IF(ISBLANK(D63), "", _xlfn.CONCAT("T", TEXT(B63, "0000"), "/", VLOOKUP(D63, Internal!$B$35:C$39, 2, FALSE), IF(OR(D63="QA", D63="Revision"), _xlfn.CONCAT("/", H63), "")))</f>
-        <v/>
-      </c>
-      <c r="D63" s="44"/>
-      <c r="E63" s="43"/>
-      <c r="F63" s="43"/>
-      <c r="G63" s="44"/>
-      <c r="H63" s="43"/>
-      <c r="I63" s="46"/>
-      <c r="J63" s="46"/>
+        <v>T0053/D</v>
+      </c>
+      <c r="D63" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E63" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F63" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G63" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H63" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="I63" s="46">
+        <v>46144</v>
+      </c>
+      <c r="J63" s="46">
+        <v>46144.999305555553</v>
+      </c>
       <c r="K63" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L63" s="47"/>
-      <c r="M63" s="47"/>
-      <c r="N63" s="45" t="str">
+        <f ca="1">IF(OR(I63="",J63=""),"",IF(AND(J63&lt;&gt;"",I63&gt;=NOW()),"Planned",IF(AND(J63&lt;&gt;"",J63&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L63" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M63" s="47">
+        <v>0.35</v>
+      </c>
+      <c r="N63" s="45">
         <f>IF(ISBLANK(L63), "", L63*VLOOKUP($F63,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O63" s="45" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="O63" s="45">
         <f>IF(ISBLANK(M63), "", M63*VLOOKUP($F63,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P63" s="44"/>
+        <v>8.75</v>
+      </c>
+      <c r="P63" s="44" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B64" s="41">
@@ -9537,30 +10185,50 @@
       </c>
       <c r="C64" s="42" t="str">
         <f>IF(ISBLANK(D64), "", _xlfn.CONCAT("T", TEXT(B64, "0000"), "/", VLOOKUP(D64, Internal!$B$35:C$39, 2, FALSE), IF(OR(D64="QA", D64="Revision"), _xlfn.CONCAT("/", H64), "")))</f>
-        <v/>
-      </c>
-      <c r="D64" s="44"/>
-      <c r="E64" s="43"/>
-      <c r="F64" s="43"/>
-      <c r="G64" s="44"/>
-      <c r="H64" s="43"/>
-      <c r="I64" s="46"/>
-      <c r="J64" s="46"/>
+        <v>T0054/D</v>
+      </c>
+      <c r="D64" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E64" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F64" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H64" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="I64" s="46">
+        <v>46145</v>
+      </c>
+      <c r="J64" s="46">
+        <v>46145.999305555553</v>
+      </c>
       <c r="K64" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L64" s="47"/>
-      <c r="M64" s="47"/>
-      <c r="N64" s="45" t="str">
+        <f ca="1">IF(OR(I64="",J64=""),"",IF(AND(J64&lt;&gt;"",I64&gt;=NOW()),"Planned",IF(AND(J64&lt;&gt;"",J64&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L64" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M64" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N64" s="45">
         <f>IF(ISBLANK(L64), "", L64*VLOOKUP($F64,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O64" s="45" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="O64" s="45">
         <f>IF(ISBLANK(M64), "", M64*VLOOKUP($F64,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P64" s="44"/>
+        <v>6.25</v>
+      </c>
+      <c r="P64" s="44" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="41">
@@ -9568,30 +10236,50 @@
       </c>
       <c r="C65" s="42" t="str">
         <f>IF(ISBLANK(D65), "", _xlfn.CONCAT("T", TEXT(B65, "0000"), "/", VLOOKUP(D65, Internal!$B$35:C$39, 2, FALSE), IF(OR(D65="QA", D65="Revision"), _xlfn.CONCAT("/", H65), "")))</f>
-        <v/>
-      </c>
-      <c r="D65" s="44"/>
-      <c r="E65" s="43"/>
-      <c r="F65" s="43"/>
-      <c r="G65" s="44"/>
-      <c r="H65" s="43"/>
-      <c r="I65" s="46"/>
-      <c r="J65" s="46"/>
+        <v>T0055/D</v>
+      </c>
+      <c r="D65" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E65" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F65" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G65" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H65" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="I65" s="46">
+        <v>46147</v>
+      </c>
+      <c r="J65" s="46">
+        <v>46147.999305555553</v>
+      </c>
       <c r="K65" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L65" s="47"/>
-      <c r="M65" s="47"/>
-      <c r="N65" s="45" t="str">
+        <f t="shared" ref="K65:K75" ca="1" si="0">IF(OR(I65="",J65=""),"",IF(AND(J65&lt;&gt;"",I65&gt;=NOW()),"Planned",IF(AND(J65&lt;&gt;"",J65&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L65" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M65" s="47">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="N65" s="45">
         <f>IF(ISBLANK(L65), "", L65*VLOOKUP($F65,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O65" s="45" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="O65" s="45">
         <f>IF(ISBLANK(M65), "", M65*VLOOKUP($F65,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P65" s="44"/>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="P65" s="44" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="41">
@@ -9599,30 +10287,50 @@
       </c>
       <c r="C66" s="42" t="str">
         <f>IF(ISBLANK(D66), "", _xlfn.CONCAT("T", TEXT(B66, "0000"), "/", VLOOKUP(D66, Internal!$B$35:C$39, 2, FALSE), IF(OR(D66="QA", D66="Revision"), _xlfn.CONCAT("/", H66), "")))</f>
-        <v/>
-      </c>
-      <c r="D66" s="44"/>
-      <c r="E66" s="43"/>
-      <c r="F66" s="43"/>
-      <c r="G66" s="44"/>
-      <c r="H66" s="43"/>
-      <c r="I66" s="46"/>
-      <c r="J66" s="46"/>
+        <v>T0056/D</v>
+      </c>
+      <c r="D66" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E66" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F66" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G66" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H66" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="I66" s="46">
+        <v>46145.864583333336</v>
+      </c>
+      <c r="J66" s="46">
+        <v>46145.999305555553</v>
+      </c>
       <c r="K66" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L66" s="47"/>
-      <c r="M66" s="47"/>
-      <c r="N66" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L66" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M66" s="47">
+        <v>0.08</v>
+      </c>
+      <c r="N66" s="45">
         <f>IF(ISBLANK(L66), "", L66*VLOOKUP($F66,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O66" s="45" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="O66" s="45">
         <f>IF(ISBLANK(M66), "", M66*VLOOKUP($F66,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P66" s="44"/>
+        <v>2</v>
+      </c>
+      <c r="P66" s="44" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="41">
@@ -9630,30 +10338,50 @@
       </c>
       <c r="C67" s="42" t="str">
         <f>IF(ISBLANK(D67), "", _xlfn.CONCAT("T", TEXT(B67, "0000"), "/", VLOOKUP(D67, Internal!$B$35:C$39, 2, FALSE), IF(OR(D67="QA", D67="Revision"), _xlfn.CONCAT("/", H67), "")))</f>
-        <v/>
-      </c>
-      <c r="D67" s="44"/>
-      <c r="E67" s="43"/>
-      <c r="F67" s="43"/>
-      <c r="G67" s="44"/>
-      <c r="H67" s="43"/>
-      <c r="I67" s="46"/>
-      <c r="J67" s="46"/>
+        <v>T0057/D</v>
+      </c>
+      <c r="D67" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E67" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F67" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G67" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H67" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="I67" s="46">
+        <v>46145.665972222225</v>
+      </c>
+      <c r="J67" s="46">
+        <v>46145.999305555553</v>
+      </c>
       <c r="K67" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L67" s="47"/>
-      <c r="M67" s="47"/>
-      <c r="N67" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L67" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M67" s="47">
+        <v>0.45</v>
+      </c>
+      <c r="N67" s="45">
         <f>IF(ISBLANK(L67), "", L67*VLOOKUP($F67,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O67" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O67" s="45">
         <f>IF(ISBLANK(M67), "", M67*VLOOKUP($F67,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P67" s="44"/>
+        <v>11.25</v>
+      </c>
+      <c r="P67" s="44" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="41">
@@ -9661,30 +10389,50 @@
       </c>
       <c r="C68" s="42" t="str">
         <f>IF(ISBLANK(D68), "", _xlfn.CONCAT("T", TEXT(B68, "0000"), "/", VLOOKUP(D68, Internal!$B$35:C$39, 2, FALSE), IF(OR(D68="QA", D68="Revision"), _xlfn.CONCAT("/", H68), "")))</f>
-        <v/>
-      </c>
-      <c r="D68" s="44"/>
-      <c r="E68" s="43"/>
-      <c r="F68" s="43"/>
-      <c r="G68" s="44"/>
-      <c r="H68" s="43"/>
-      <c r="I68" s="46"/>
-      <c r="J68" s="46"/>
+        <v>T0058/D</v>
+      </c>
+      <c r="D68" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E68" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F68" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G68" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H68" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="I68" s="46">
+        <v>46143</v>
+      </c>
+      <c r="J68" s="46">
+        <v>46143.999305555553</v>
+      </c>
       <c r="K68" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L68" s="47"/>
-      <c r="M68" s="47"/>
-      <c r="N68" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L68" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M68" s="47">
+        <v>0.67</v>
+      </c>
+      <c r="N68" s="45">
         <f>IF(ISBLANK(L68), "", L68*VLOOKUP($F68,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O68" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O68" s="45">
         <f>IF(ISBLANK(M68), "", M68*VLOOKUP($F68,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P68" s="44"/>
+        <v>16.75</v>
+      </c>
+      <c r="P68" s="44" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B69" s="41">
@@ -9692,30 +10440,48 @@
       </c>
       <c r="C69" s="42" t="str">
         <f>IF(ISBLANK(D69), "", _xlfn.CONCAT("T", TEXT(B69, "0000"), "/", VLOOKUP(D69, Internal!$B$35:C$39, 2, FALSE), IF(OR(D69="QA", D69="Revision"), _xlfn.CONCAT("/", H69), "")))</f>
-        <v/>
-      </c>
-      <c r="D69" s="44"/>
-      <c r="E69" s="43"/>
-      <c r="F69" s="43"/>
-      <c r="G69" s="44"/>
+        <v>T0059/M</v>
+      </c>
+      <c r="D69" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E69" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F69" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" s="44" t="s">
+        <v>20</v>
+      </c>
       <c r="H69" s="43"/>
-      <c r="I69" s="46"/>
-      <c r="J69" s="46"/>
+      <c r="I69" s="46">
+        <v>46125</v>
+      </c>
+      <c r="J69" s="46">
+        <v>46125.999305555553</v>
+      </c>
       <c r="K69" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L69" s="47"/>
-      <c r="M69" s="47"/>
-      <c r="N69" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L69" s="47">
+        <v>3</v>
+      </c>
+      <c r="M69" s="47">
+        <v>3.5</v>
+      </c>
+      <c r="N69" s="45">
         <f>IF(ISBLANK(L69), "", L69*VLOOKUP($F69,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O69" s="45" t="str">
+        <v>150</v>
+      </c>
+      <c r="O69" s="45">
         <f>IF(ISBLANK(M69), "", M69*VLOOKUP($F69,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P69" s="44"/>
+        <v>175</v>
+      </c>
+      <c r="P69" s="44" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B70" s="41">
@@ -9723,30 +10489,48 @@
       </c>
       <c r="C70" s="42" t="str">
         <f>IF(ISBLANK(D70), "", _xlfn.CONCAT("T", TEXT(B70, "0000"), "/", VLOOKUP(D70, Internal!$B$35:C$39, 2, FALSE), IF(OR(D70="QA", D70="Revision"), _xlfn.CONCAT("/", H70), "")))</f>
-        <v/>
-      </c>
-      <c r="D70" s="44"/>
-      <c r="E70" s="43"/>
-      <c r="F70" s="43"/>
-      <c r="G70" s="44"/>
+        <v>T0060/M</v>
+      </c>
+      <c r="D70" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E70" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F70" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G70" s="44" t="s">
+        <v>33</v>
+      </c>
       <c r="H70" s="43"/>
-      <c r="I70" s="46"/>
-      <c r="J70" s="46"/>
+      <c r="I70" s="46">
+        <v>46146.520833333336</v>
+      </c>
+      <c r="J70" s="46">
+        <v>46146.999305555553</v>
+      </c>
       <c r="K70" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L70" s="47"/>
-      <c r="M70" s="47"/>
-      <c r="N70" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L70" s="47">
+        <v>2.5</v>
+      </c>
+      <c r="M70" s="47">
+        <v>2</v>
+      </c>
+      <c r="N70" s="45">
         <f>IF(ISBLANK(L70), "", L70*VLOOKUP($F70,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O70" s="45" t="str">
+        <v>125</v>
+      </c>
+      <c r="O70" s="45">
         <f>IF(ISBLANK(M70), "", M70*VLOOKUP($F70,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P70" s="44"/>
+        <v>100</v>
+      </c>
+      <c r="P70" s="44" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="41">
@@ -9754,30 +10538,48 @@
       </c>
       <c r="C71" s="42" t="str">
         <f>IF(ISBLANK(D71), "", _xlfn.CONCAT("T", TEXT(B71, "0000"), "/", VLOOKUP(D71, Internal!$B$35:C$39, 2, FALSE), IF(OR(D71="QA", D71="Revision"), _xlfn.CONCAT("/", H71), "")))</f>
-        <v/>
-      </c>
-      <c r="D71" s="44"/>
-      <c r="E71" s="43"/>
-      <c r="F71" s="43"/>
-      <c r="G71" s="44"/>
+        <v>T0061/D</v>
+      </c>
+      <c r="D71" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E71" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F71" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G71" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H71" s="43"/>
-      <c r="I71" s="46"/>
-      <c r="J71" s="46"/>
+      <c r="I71" s="46">
+        <v>46146.520833333336</v>
+      </c>
+      <c r="J71" s="46">
+        <v>46148.999305555553</v>
+      </c>
       <c r="K71" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L71" s="47"/>
-      <c r="M71" s="47"/>
-      <c r="N71" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L71" s="47">
+        <v>2</v>
+      </c>
+      <c r="M71" s="47">
+        <v>1.9</v>
+      </c>
+      <c r="N71" s="45">
         <f>IF(ISBLANK(L71), "", L71*VLOOKUP($F71,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O71" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O71" s="45">
         <f>IF(ISBLANK(M71), "", M71*VLOOKUP($F71,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P71" s="44"/>
+        <v>47.5</v>
+      </c>
+      <c r="P71" s="44" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B72" s="41">
@@ -9785,30 +10587,48 @@
       </c>
       <c r="C72" s="42" t="str">
         <f>IF(ISBLANK(D72), "", _xlfn.CONCAT("T", TEXT(B72, "0000"), "/", VLOOKUP(D72, Internal!$B$35:C$39, 2, FALSE), IF(OR(D72="QA", D72="Revision"), _xlfn.CONCAT("/", H72), "")))</f>
-        <v/>
-      </c>
-      <c r="D72" s="44"/>
-      <c r="E72" s="43"/>
-      <c r="F72" s="43"/>
-      <c r="G72" s="44"/>
+        <v>T0062/M</v>
+      </c>
+      <c r="D72" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E72" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F72" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G72" s="44" t="s">
+        <v>33</v>
+      </c>
       <c r="H72" s="43"/>
-      <c r="I72" s="46"/>
-      <c r="J72" s="46"/>
+      <c r="I72" s="46">
+        <v>46149.722222222219</v>
+      </c>
+      <c r="J72" s="46">
+        <v>46149.736111111109</v>
+      </c>
       <c r="K72" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L72" s="47"/>
-      <c r="M72" s="47"/>
-      <c r="N72" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L72" s="47">
+        <v>0.33</v>
+      </c>
+      <c r="M72" s="47">
+        <v>0.33</v>
+      </c>
+      <c r="N72" s="45">
         <f>IF(ISBLANK(L72), "", L72*VLOOKUP($F72,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O72" s="45" t="str">
+        <v>16.5</v>
+      </c>
+      <c r="O72" s="45">
         <f>IF(ISBLANK(M72), "", M72*VLOOKUP($F72,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P72" s="44"/>
+        <v>16.5</v>
+      </c>
+      <c r="P72" s="44" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B73" s="41">
@@ -9816,30 +10636,48 @@
       </c>
       <c r="C73" s="42" t="str">
         <f>IF(ISBLANK(D73), "", _xlfn.CONCAT("T", TEXT(B73, "0000"), "/", VLOOKUP(D73, Internal!$B$35:C$39, 2, FALSE), IF(OR(D73="QA", D73="Revision"), _xlfn.CONCAT("/", H73), "")))</f>
-        <v/>
-      </c>
-      <c r="D73" s="44"/>
-      <c r="E73" s="43"/>
-      <c r="F73" s="43"/>
-      <c r="G73" s="44"/>
+        <v>T0063/D</v>
+      </c>
+      <c r="D73" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E73" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F73" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G73" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H73" s="43"/>
-      <c r="I73" s="46"/>
-      <c r="J73" s="46"/>
+      <c r="I73" s="46">
+        <v>46149.736111111109</v>
+      </c>
+      <c r="J73" s="46">
+        <v>46149.902777777781</v>
+      </c>
       <c r="K73" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L73" s="47"/>
-      <c r="M73" s="47"/>
-      <c r="N73" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L73" s="47">
+        <v>4</v>
+      </c>
+      <c r="M73" s="47">
+        <v>4</v>
+      </c>
+      <c r="N73" s="45">
         <f>IF(ISBLANK(L73), "", L73*VLOOKUP($F73,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O73" s="45" t="str">
+        <v>100</v>
+      </c>
+      <c r="O73" s="45">
         <f>IF(ISBLANK(M73), "", M73*VLOOKUP($F73,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P73" s="44"/>
+        <v>100</v>
+      </c>
+      <c r="P73" s="44" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B74" s="41">
@@ -9847,30 +10685,50 @@
       </c>
       <c r="C74" s="42" t="str">
         <f>IF(ISBLANK(D74), "", _xlfn.CONCAT("T", TEXT(B74, "0000"), "/", VLOOKUP(D74, Internal!$B$35:C$39, 2, FALSE), IF(OR(D74="QA", D74="Revision"), _xlfn.CONCAT("/", H74), "")))</f>
-        <v/>
-      </c>
-      <c r="D74" s="44"/>
-      <c r="E74" s="43"/>
-      <c r="F74" s="43"/>
-      <c r="G74" s="44"/>
-      <c r="H74" s="43"/>
-      <c r="I74" s="46"/>
-      <c r="J74" s="46"/>
+        <v>T0064/D</v>
+      </c>
+      <c r="D74" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E74" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F74" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G74" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H74" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="I74" s="46">
+        <v>46149.902777777781</v>
+      </c>
+      <c r="J74" s="46">
+        <v>46149.913194444445</v>
+      </c>
       <c r="K74" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L74" s="47"/>
-      <c r="M74" s="47"/>
-      <c r="N74" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L74" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M74" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="N74" s="45">
         <f>IF(ISBLANK(L74), "", L74*VLOOKUP($F74,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O74" s="45" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="O74" s="45">
         <f>IF(ISBLANK(M74), "", M74*VLOOKUP($F74,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P74" s="44"/>
+        <v>6.25</v>
+      </c>
+      <c r="P74" s="44" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B75" s="41">
@@ -9878,30 +10736,48 @@
       </c>
       <c r="C75" s="42" t="str">
         <f>IF(ISBLANK(D75), "", _xlfn.CONCAT("T", TEXT(B75, "0000"), "/", VLOOKUP(D75, Internal!$B$35:C$39, 2, FALSE), IF(OR(D75="QA", D75="Revision"), _xlfn.CONCAT("/", H75), "")))</f>
-        <v/>
-      </c>
-      <c r="D75" s="44"/>
-      <c r="E75" s="43"/>
-      <c r="F75" s="43"/>
-      <c r="G75" s="44"/>
+        <v>T0065/D</v>
+      </c>
+      <c r="D75" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E75" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F75" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G75" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H75" s="43"/>
-      <c r="I75" s="46"/>
-      <c r="J75" s="46"/>
+      <c r="I75" s="46">
+        <v>46149.902777777781</v>
+      </c>
+      <c r="J75" s="46">
+        <v>46149.923611111109</v>
+      </c>
       <c r="K75" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L75" s="47"/>
-      <c r="M75" s="47"/>
-      <c r="N75" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L75" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M75" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="N75" s="45">
         <f>IF(ISBLANK(L75), "", L75*VLOOKUP($F75,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O75" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O75" s="45">
         <f>IF(ISBLANK(M75), "", M75*VLOOKUP($F75,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P75" s="44"/>
+        <v>12.5</v>
+      </c>
+      <c r="P75" s="44" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="41">
@@ -9909,30 +10785,50 @@
       </c>
       <c r="C76" s="42" t="str">
         <f>IF(ISBLANK(D76), "", _xlfn.CONCAT("T", TEXT(B76, "0000"), "/", VLOOKUP(D76, Internal!$B$35:C$39, 2, FALSE), IF(OR(D76="QA", D76="Revision"), _xlfn.CONCAT("/", H76), "")))</f>
-        <v/>
-      </c>
-      <c r="D76" s="44"/>
-      <c r="E76" s="43"/>
-      <c r="F76" s="43"/>
-      <c r="G76" s="44"/>
-      <c r="H76" s="43"/>
-      <c r="I76" s="46"/>
-      <c r="J76" s="46"/>
+        <v>T0066/D</v>
+      </c>
+      <c r="D76" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E76" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F76" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G76" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H76" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="I76" s="46">
+        <v>46149.923611111109</v>
+      </c>
+      <c r="J76" s="46">
+        <v>46149.930555555555</v>
+      </c>
       <c r="K76" s="45" t="str">
         <f t="shared" ref="K76:K110" ca="1" si="1">IF(OR(I76="",J76=""),"",IF(AND(J76&lt;&gt;"",I76&gt;=NOW()),"Planned",IF(AND(J76&lt;&gt;"",J76&lt;NOW()),"Completed","Ongoing")))</f>
-        <v/>
-      </c>
-      <c r="L76" s="47"/>
-      <c r="M76" s="47"/>
-      <c r="N76" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L76" s="47">
+        <v>0.17</v>
+      </c>
+      <c r="M76" s="47">
+        <v>0.17</v>
+      </c>
+      <c r="N76" s="45">
         <f>IF(ISBLANK(L76), "", L76*VLOOKUP($F76,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O76" s="45" t="str">
+        <v>4.25</v>
+      </c>
+      <c r="O76" s="45">
         <f>IF(ISBLANK(M76), "", M76*VLOOKUP($F76,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P76" s="44"/>
+        <v>4.25</v>
+      </c>
+      <c r="P76" s="44" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B77" s="41">
@@ -9940,30 +10836,48 @@
       </c>
       <c r="C77" s="42" t="str">
         <f>IF(ISBLANK(D77), "", _xlfn.CONCAT("T", TEXT(B77, "0000"), "/", VLOOKUP(D77, Internal!$B$35:C$39, 2, FALSE), IF(OR(D77="QA", D77="Revision"), _xlfn.CONCAT("/", H77), "")))</f>
-        <v/>
-      </c>
-      <c r="D77" s="44"/>
-      <c r="E77" s="43"/>
-      <c r="F77" s="43"/>
-      <c r="G77" s="44"/>
+        <v>T0067/D</v>
+      </c>
+      <c r="D77" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F77" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G77" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H77" s="43"/>
-      <c r="I77" s="46"/>
-      <c r="J77" s="46"/>
+      <c r="I77" s="46">
+        <v>46149.902777777781</v>
+      </c>
+      <c r="J77" s="46">
+        <v>46149.923611111109</v>
+      </c>
       <c r="K77" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L77" s="47"/>
-      <c r="M77" s="47"/>
-      <c r="N77" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L77" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M77" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="N77" s="45">
         <f>IF(ISBLANK(L77), "", L77*VLOOKUP($F77,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O77" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O77" s="45">
         <f>IF(ISBLANK(M77), "", M77*VLOOKUP($F77,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P77" s="44"/>
+        <v>12.5</v>
+      </c>
+      <c r="P77" s="44" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B78" s="41">
@@ -9971,30 +10885,50 @@
       </c>
       <c r="C78" s="42" t="str">
         <f>IF(ISBLANK(D78), "", _xlfn.CONCAT("T", TEXT(B78, "0000"), "/", VLOOKUP(D78, Internal!$B$35:C$39, 2, FALSE), IF(OR(D78="QA", D78="Revision"), _xlfn.CONCAT("/", H78), "")))</f>
-        <v/>
-      </c>
-      <c r="D78" s="44"/>
-      <c r="E78" s="43"/>
-      <c r="F78" s="43"/>
-      <c r="G78" s="44"/>
-      <c r="H78" s="43"/>
-      <c r="I78" s="46"/>
-      <c r="J78" s="46"/>
+        <v>T0068/D</v>
+      </c>
+      <c r="D78" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E78" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F78" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G78" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H78" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="I78" s="46">
+        <v>46149.930555555555</v>
+      </c>
+      <c r="J78" s="46">
+        <v>46149.930555555555</v>
+      </c>
       <c r="K78" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L78" s="47"/>
-      <c r="M78" s="47"/>
-      <c r="N78" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L78" s="47">
+        <v>0.17</v>
+      </c>
+      <c r="M78" s="47">
+        <v>0.17</v>
+      </c>
+      <c r="N78" s="45">
         <f>IF(ISBLANK(L78), "", L78*VLOOKUP($F78,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O78" s="45" t="str">
+        <v>4.25</v>
+      </c>
+      <c r="O78" s="45">
         <f>IF(ISBLANK(M78), "", M78*VLOOKUP($F78,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P78" s="44"/>
+        <v>4.25</v>
+      </c>
+      <c r="P78" s="44" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="41">
@@ -10002,30 +10936,50 @@
       </c>
       <c r="C79" s="42" t="str">
         <f>IF(ISBLANK(D79), "", _xlfn.CONCAT("T", TEXT(B79, "0000"), "/", VLOOKUP(D79, Internal!$B$35:C$39, 2, FALSE), IF(OR(D79="QA", D79="Revision"), _xlfn.CONCAT("/", H79), "")))</f>
-        <v/>
-      </c>
-      <c r="D79" s="44"/>
-      <c r="E79" s="43"/>
-      <c r="F79" s="43"/>
-      <c r="G79" s="44"/>
-      <c r="H79" s="43"/>
-      <c r="I79" s="46"/>
-      <c r="J79" s="46"/>
+        <v>T0069/QA/T0063/D</v>
+      </c>
+      <c r="D79" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E79" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F79" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="H79" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="I79" s="46">
+        <v>46149.944444444445</v>
+      </c>
+      <c r="J79" s="46">
+        <v>46150.229166666664</v>
+      </c>
       <c r="K79" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L79" s="47"/>
-      <c r="M79" s="47"/>
-      <c r="N79" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L79" s="47">
+        <v>1</v>
+      </c>
+      <c r="M79" s="47">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="N79" s="45">
         <f>IF(ISBLANK(L79), "", L79*VLOOKUP($F79,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O79" s="45" t="str">
+        <v>30</v>
+      </c>
+      <c r="O79" s="45">
         <f>IF(ISBLANK(M79), "", M79*VLOOKUP($F79,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P79" s="44"/>
+        <v>34.5</v>
+      </c>
+      <c r="P79" s="44" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B80" s="41">
@@ -10033,30 +10987,50 @@
       </c>
       <c r="C80" s="42" t="str">
         <f>IF(ISBLANK(D80), "", _xlfn.CONCAT("T", TEXT(B80, "0000"), "/", VLOOKUP(D80, Internal!$B$35:C$39, 2, FALSE), IF(OR(D80="QA", D80="Revision"), _xlfn.CONCAT("/", H80), "")))</f>
-        <v/>
-      </c>
-      <c r="D80" s="44"/>
-      <c r="E80" s="43"/>
-      <c r="F80" s="43"/>
-      <c r="G80" s="44"/>
-      <c r="H80" s="43"/>
-      <c r="I80" s="46"/>
-      <c r="J80" s="46"/>
+        <v>T0070/QA/T0012/D</v>
+      </c>
+      <c r="D80" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E80" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F80" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="H80" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="I80" s="46">
+        <v>46149.944444444445</v>
+      </c>
+      <c r="J80" s="46">
+        <v>46150.229166666664</v>
+      </c>
       <c r="K80" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L80" s="47"/>
-      <c r="M80" s="47"/>
-      <c r="N80" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L80" s="47">
+        <v>2</v>
+      </c>
+      <c r="M80" s="47">
+        <v>2.5</v>
+      </c>
+      <c r="N80" s="45">
         <f>IF(ISBLANK(L80), "", L80*VLOOKUP($F80,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O80" s="45" t="str">
+        <v>60</v>
+      </c>
+      <c r="O80" s="45">
         <f>IF(ISBLANK(M80), "", M80*VLOOKUP($F80,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P80" s="44"/>
+        <v>75</v>
+      </c>
+      <c r="P80" s="44" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B81" s="41">
@@ -10064,30 +11038,50 @@
       </c>
       <c r="C81" s="42" t="str">
         <f>IF(ISBLANK(D81), "", _xlfn.CONCAT("T", TEXT(B81, "0000"), "/", VLOOKUP(D81, Internal!$B$35:C$39, 2, FALSE), IF(OR(D81="QA", D81="Revision"), _xlfn.CONCAT("/", H81), "")))</f>
-        <v/>
-      </c>
-      <c r="D81" s="44"/>
-      <c r="E81" s="43"/>
-      <c r="F81" s="43"/>
-      <c r="G81" s="44"/>
-      <c r="H81" s="43"/>
-      <c r="I81" s="46"/>
-      <c r="J81" s="46"/>
+        <v>T0071/QA/T0030/D</v>
+      </c>
+      <c r="D81" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E81" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F81" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="H81" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="I81" s="46">
+        <v>46149.944444444445</v>
+      </c>
+      <c r="J81" s="46">
+        <v>46150.229166666664</v>
+      </c>
       <c r="K81" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L81" s="47"/>
-      <c r="M81" s="47"/>
-      <c r="N81" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L81" s="47">
+        <v>0.75</v>
+      </c>
+      <c r="M81" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="N81" s="45">
         <f>IF(ISBLANK(L81), "", L81*VLOOKUP($F81,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O81" s="45" t="str">
+        <v>22.5</v>
+      </c>
+      <c r="O81" s="45">
         <f>IF(ISBLANK(M81), "", M81*VLOOKUP($F81,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P81" s="44"/>
+        <v>15</v>
+      </c>
+      <c r="P81" s="44" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B82" s="41">
@@ -10095,30 +11089,50 @@
       </c>
       <c r="C82" s="42" t="str">
         <f>IF(ISBLANK(D82), "", _xlfn.CONCAT("T", TEXT(B82, "0000"), "/", VLOOKUP(D82, Internal!$B$35:C$39, 2, FALSE), IF(OR(D82="QA", D82="Revision"), _xlfn.CONCAT("/", H82), "")))</f>
-        <v/>
-      </c>
-      <c r="D82" s="44"/>
-      <c r="E82" s="43"/>
-      <c r="F82" s="43"/>
-      <c r="G82" s="44"/>
-      <c r="H82" s="43"/>
-      <c r="I82" s="46"/>
-      <c r="J82" s="46"/>
+        <v>T0072/QA/T0017/D</v>
+      </c>
+      <c r="D82" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E82" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F82" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="H82" s="43" t="s">
+        <v>264</v>
+      </c>
+      <c r="I82" s="46">
+        <v>46149.944444444445</v>
+      </c>
+      <c r="J82" s="46">
+        <v>46150.229166666664</v>
+      </c>
       <c r="K82" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L82" s="47"/>
-      <c r="M82" s="47"/>
-      <c r="N82" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L82" s="47">
+        <v>1</v>
+      </c>
+      <c r="M82" s="47">
+        <v>0.9</v>
+      </c>
+      <c r="N82" s="45">
         <f>IF(ISBLANK(L82), "", L82*VLOOKUP($F82,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O82" s="45" t="str">
+        <v>30</v>
+      </c>
+      <c r="O82" s="45">
         <f>IF(ISBLANK(M82), "", M82*VLOOKUP($F82,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P82" s="44"/>
+        <v>27</v>
+      </c>
+      <c r="P82" s="44" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B83" s="41">
@@ -10126,30 +11140,48 @@
       </c>
       <c r="C83" s="42" t="str">
         <f>IF(ISBLANK(D83), "", _xlfn.CONCAT("T", TEXT(B83, "0000"), "/", VLOOKUP(D83, Internal!$B$35:C$39, 2, FALSE), IF(OR(D83="QA", D83="Revision"), _xlfn.CONCAT("/", H83), "")))</f>
-        <v/>
-      </c>
-      <c r="D83" s="44"/>
-      <c r="E83" s="43"/>
-      <c r="F83" s="43"/>
-      <c r="G83" s="44"/>
+        <v>T0073/D</v>
+      </c>
+      <c r="D83" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E83" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F83" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G83" s="44" t="s">
+        <v>36</v>
+      </c>
       <c r="H83" s="43"/>
-      <c r="I83" s="46"/>
-      <c r="J83" s="46"/>
+      <c r="I83" s="46">
+        <v>46150.354166666664</v>
+      </c>
+      <c r="J83" s="46">
+        <v>46150.402777777781</v>
+      </c>
       <c r="K83" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L83" s="47"/>
-      <c r="M83" s="47"/>
-      <c r="N83" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L83" s="47">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M83" s="47">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N83" s="45">
         <f>IF(ISBLANK(L83), "", L83*VLOOKUP($F83,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O83" s="45" t="str">
+        <v>44</v>
+      </c>
+      <c r="O83" s="45">
         <f>IF(ISBLANK(M83), "", M83*VLOOKUP($F83,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P83" s="44"/>
+        <v>44</v>
+      </c>
+      <c r="P83" s="44" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B84" s="41">
@@ -10157,30 +11189,48 @@
       </c>
       <c r="C84" s="42" t="str">
         <f>IF(ISBLANK(D84), "", _xlfn.CONCAT("T", TEXT(B84, "0000"), "/", VLOOKUP(D84, Internal!$B$35:C$39, 2, FALSE), IF(OR(D84="QA", D84="Revision"), _xlfn.CONCAT("/", H84), "")))</f>
-        <v/>
-      </c>
-      <c r="D84" s="44"/>
-      <c r="E84" s="43"/>
-      <c r="F84" s="43"/>
-      <c r="G84" s="44"/>
+        <v>T0074/QA/</v>
+      </c>
+      <c r="D84" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E84" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F84" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G84" s="44" t="s">
+        <v>36</v>
+      </c>
       <c r="H84" s="43"/>
-      <c r="I84" s="46"/>
-      <c r="J84" s="46"/>
+      <c r="I84" s="46">
+        <v>46150.444444444445</v>
+      </c>
+      <c r="J84" s="46">
+        <v>46150.520833333336</v>
+      </c>
       <c r="K84" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L84" s="47"/>
-      <c r="M84" s="47"/>
-      <c r="N84" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L84" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="M84" s="47">
+        <v>1.83</v>
+      </c>
+      <c r="N84" s="45">
         <f>IF(ISBLANK(L84), "", L84*VLOOKUP($F84,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O84" s="45" t="str">
+        <v>45.75</v>
+      </c>
+      <c r="O84" s="45">
         <f>IF(ISBLANK(M84), "", M84*VLOOKUP($F84,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P84" s="44"/>
+        <v>45.75</v>
+      </c>
+      <c r="P84" s="44" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B85" s="41">
@@ -10188,30 +11238,48 @@
       </c>
       <c r="C85" s="42" t="str">
         <f>IF(ISBLANK(D85), "", _xlfn.CONCAT("T", TEXT(B85, "0000"), "/", VLOOKUP(D85, Internal!$B$35:C$39, 2, FALSE), IF(OR(D85="QA", D85="Revision"), _xlfn.CONCAT("/", H85), "")))</f>
-        <v/>
-      </c>
-      <c r="D85" s="44"/>
-      <c r="E85" s="43"/>
-      <c r="F85" s="43"/>
-      <c r="G85" s="44"/>
+        <v>T0075/QA/</v>
+      </c>
+      <c r="D85" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E85" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F85" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G85" s="44" t="s">
+        <v>36</v>
+      </c>
       <c r="H85" s="43"/>
-      <c r="I85" s="46"/>
-      <c r="J85" s="46"/>
+      <c r="I85" s="46">
+        <v>46150.520833333336</v>
+      </c>
+      <c r="J85" s="46">
+        <v>46150.5625</v>
+      </c>
       <c r="K85" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L85" s="47"/>
-      <c r="M85" s="47"/>
-      <c r="N85" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L85" s="47">
+        <v>1</v>
+      </c>
+      <c r="M85" s="47">
+        <v>1</v>
+      </c>
+      <c r="N85" s="45">
         <f>IF(ISBLANK(L85), "", L85*VLOOKUP($F85,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O85" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O85" s="45">
         <f>IF(ISBLANK(M85), "", M85*VLOOKUP($F85,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P85" s="44"/>
+        <v>25</v>
+      </c>
+      <c r="P85" s="44" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B86" s="41">
@@ -10219,30 +11287,48 @@
       </c>
       <c r="C86" s="42" t="str">
         <f>IF(ISBLANK(D86), "", _xlfn.CONCAT("T", TEXT(B86, "0000"), "/", VLOOKUP(D86, Internal!$B$35:C$39, 2, FALSE), IF(OR(D86="QA", D86="Revision"), _xlfn.CONCAT("/", H86), "")))</f>
-        <v/>
-      </c>
-      <c r="D86" s="44"/>
-      <c r="E86" s="43"/>
-      <c r="F86" s="43"/>
-      <c r="G86" s="44"/>
+        <v>T0076/D</v>
+      </c>
+      <c r="D86" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E86" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F86" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G86" s="44" t="s">
+        <v>41</v>
+      </c>
       <c r="H86" s="43"/>
-      <c r="I86" s="46"/>
-      <c r="J86" s="46"/>
+      <c r="I86" s="46">
+        <v>46150.5625</v>
+      </c>
+      <c r="J86" s="46">
+        <v>46150.75</v>
+      </c>
       <c r="K86" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L86" s="47"/>
-      <c r="M86" s="47"/>
-      <c r="N86" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L86" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="M86" s="47">
+        <v>1.25</v>
+      </c>
+      <c r="N86" s="45">
         <f>IF(ISBLANK(L86), "", L86*VLOOKUP($F86,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O86" s="45" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="O86" s="45">
         <f>IF(ISBLANK(M86), "", M86*VLOOKUP($F86,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P86" s="44"/>
+        <v>31.25</v>
+      </c>
+      <c r="P86" s="44" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B87" s="41">
@@ -10250,30 +11336,50 @@
       </c>
       <c r="C87" s="42" t="str">
         <f>IF(ISBLANK(D87), "", _xlfn.CONCAT("T", TEXT(B87, "0000"), "/", VLOOKUP(D87, Internal!$B$35:C$39, 2, FALSE), IF(OR(D87="QA", D87="Revision"), _xlfn.CONCAT("/", H87), "")))</f>
-        <v/>
-      </c>
-      <c r="D87" s="44"/>
-      <c r="E87" s="43"/>
-      <c r="F87" s="43"/>
-      <c r="G87" s="44"/>
-      <c r="H87" s="43"/>
-      <c r="I87" s="46"/>
-      <c r="J87" s="46"/>
+        <v>T0077/QA/T0034/D</v>
+      </c>
+      <c r="D87" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E87" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F87" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G87" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="H87" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="I87" s="46">
+        <v>46149.944444444445</v>
+      </c>
+      <c r="J87" s="46">
+        <v>46150.229166666664</v>
+      </c>
       <c r="K87" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L87" s="47"/>
-      <c r="M87" s="47"/>
-      <c r="N87" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L87" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M87" s="47">
+        <v>0.6</v>
+      </c>
+      <c r="N87" s="45">
         <f>IF(ISBLANK(L87), "", L87*VLOOKUP($F87,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O87" s="45" t="str">
+        <v>15</v>
+      </c>
+      <c r="O87" s="45">
         <f>IF(ISBLANK(M87), "", M87*VLOOKUP($F87,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P87" s="44"/>
+        <v>18</v>
+      </c>
+      <c r="P87" s="44" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B88" s="41">
@@ -10281,30 +11387,50 @@
       </c>
       <c r="C88" s="42" t="str">
         <f>IF(ISBLANK(D88), "", _xlfn.CONCAT("T", TEXT(B88, "0000"), "/", VLOOKUP(D88, Internal!$B$35:C$39, 2, FALSE), IF(OR(D88="QA", D88="Revision"), _xlfn.CONCAT("/", H88), "")))</f>
-        <v/>
-      </c>
-      <c r="D88" s="44"/>
-      <c r="E88" s="43"/>
-      <c r="F88" s="43"/>
-      <c r="G88" s="44"/>
-      <c r="H88" s="43"/>
-      <c r="I88" s="46"/>
-      <c r="J88" s="46"/>
+        <v>T0078/QA/T0023/D</v>
+      </c>
+      <c r="D88" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E88" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F88" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="H88" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="I88" s="46">
+        <v>46149.944444444445</v>
+      </c>
+      <c r="J88" s="46">
+        <v>46150.229166666664</v>
+      </c>
       <c r="K88" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L88" s="47"/>
-      <c r="M88" s="47"/>
-      <c r="N88" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L88" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M88" s="47">
+        <v>0.6</v>
+      </c>
+      <c r="N88" s="45">
         <f>IF(ISBLANK(L88), "", L88*VLOOKUP($F88,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O88" s="45" t="str">
+        <v>15</v>
+      </c>
+      <c r="O88" s="45">
         <f>IF(ISBLANK(M88), "", M88*VLOOKUP($F88,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P88" s="44"/>
+        <v>18</v>
+      </c>
+      <c r="P88" s="44" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B89" s="41">
@@ -10312,30 +11438,50 @@
       </c>
       <c r="C89" s="42" t="str">
         <f>IF(ISBLANK(D89), "", _xlfn.CONCAT("T", TEXT(B89, "0000"), "/", VLOOKUP(D89, Internal!$B$35:C$39, 2, FALSE), IF(OR(D89="QA", D89="Revision"), _xlfn.CONCAT("/", H89), "")))</f>
-        <v/>
-      </c>
-      <c r="D89" s="44"/>
-      <c r="E89" s="43"/>
-      <c r="F89" s="43"/>
-      <c r="G89" s="44"/>
-      <c r="H89" s="43"/>
-      <c r="I89" s="46"/>
-      <c r="J89" s="46"/>
+        <v>T0079/QA/T0021/D</v>
+      </c>
+      <c r="D89" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E89" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F89" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="H89" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="I89" s="46">
+        <v>46149.944444444445</v>
+      </c>
+      <c r="J89" s="46">
+        <v>46150.229166666664</v>
+      </c>
       <c r="K89" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L89" s="47"/>
-      <c r="M89" s="47"/>
-      <c r="N89" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L89" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M89" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="N89" s="45">
         <f>IF(ISBLANK(L89), "", L89*VLOOKUP($F89,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O89" s="45" t="str">
+        <v>15</v>
+      </c>
+      <c r="O89" s="45">
         <f>IF(ISBLANK(M89), "", M89*VLOOKUP($F89,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P89" s="44"/>
+        <v>15</v>
+      </c>
+      <c r="P89" s="44" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B90" s="41">
@@ -10343,30 +11489,50 @@
       </c>
       <c r="C90" s="42" t="str">
         <f>IF(ISBLANK(D90), "", _xlfn.CONCAT("T", TEXT(B90, "0000"), "/", VLOOKUP(D90, Internal!$B$35:C$39, 2, FALSE), IF(OR(D90="QA", D90="Revision"), _xlfn.CONCAT("/", H90), "")))</f>
-        <v/>
-      </c>
-      <c r="D90" s="44"/>
-      <c r="E90" s="43"/>
-      <c r="F90" s="43"/>
-      <c r="G90" s="44"/>
-      <c r="H90" s="43"/>
-      <c r="I90" s="46"/>
-      <c r="J90" s="46"/>
+        <v>T0080/QA/T0013/D</v>
+      </c>
+      <c r="D90" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E90" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F90" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G90" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="H90" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="I90" s="46">
+        <v>46150.5625</v>
+      </c>
+      <c r="J90" s="46">
+        <v>46150.645833333336</v>
+      </c>
       <c r="K90" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L90" s="47"/>
-      <c r="M90" s="47"/>
-      <c r="N90" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L90" s="47">
+        <v>1.25</v>
+      </c>
+      <c r="M90" s="47">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="N90" s="45">
         <f>IF(ISBLANK(L90), "", L90*VLOOKUP($F90,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O90" s="45" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="O90" s="45">
         <f>IF(ISBLANK(M90), "", M90*VLOOKUP($F90,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P90" s="44"/>
+        <v>34.5</v>
+      </c>
+      <c r="P90" s="44" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B91" s="41">
@@ -10374,30 +11540,50 @@
       </c>
       <c r="C91" s="42" t="str">
         <f>IF(ISBLANK(D91), "", _xlfn.CONCAT("T", TEXT(B91, "0000"), "/", VLOOKUP(D91, Internal!$B$35:C$39, 2, FALSE), IF(OR(D91="QA", D91="Revision"), _xlfn.CONCAT("/", H91), "")))</f>
-        <v/>
-      </c>
-      <c r="D91" s="44"/>
-      <c r="E91" s="43"/>
-      <c r="F91" s="43"/>
-      <c r="G91" s="44"/>
-      <c r="H91" s="43"/>
-      <c r="I91" s="46"/>
-      <c r="J91" s="46"/>
+        <v>T0081/D</v>
+      </c>
+      <c r="D91" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E91" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F91" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="G91" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="H91" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="I91" s="46">
+        <v>46150.775000000001</v>
+      </c>
+      <c r="J91" s="46">
+        <v>46150.791666666664</v>
+      </c>
       <c r="K91" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L91" s="47"/>
-      <c r="M91" s="47"/>
-      <c r="N91" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L91" s="47">
+        <v>0.33</v>
+      </c>
+      <c r="M91" s="47">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="N91" s="45">
         <f>IF(ISBLANK(L91), "", L91*VLOOKUP($F91,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O91" s="45" t="str">
+        <v>8.25</v>
+      </c>
+      <c r="O91" s="45">
         <f>IF(ISBLANK(M91), "", M91*VLOOKUP($F91,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P91" s="44"/>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="P91" s="44" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="41">
@@ -10405,30 +11591,48 @@
       </c>
       <c r="C92" s="42" t="str">
         <f>IF(ISBLANK(D92), "", _xlfn.CONCAT("T", TEXT(B92, "0000"), "/", VLOOKUP(D92, Internal!$B$35:C$39, 2, FALSE), IF(OR(D92="QA", D92="Revision"), _xlfn.CONCAT("/", H92), "")))</f>
-        <v/>
-      </c>
-      <c r="D92" s="44"/>
-      <c r="E92" s="43"/>
-      <c r="F92" s="43"/>
-      <c r="G92" s="44"/>
+        <v>T0082/QA/</v>
+      </c>
+      <c r="D92" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E92" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F92" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G92" s="44" t="s">
+        <v>36</v>
+      </c>
       <c r="H92" s="43"/>
-      <c r="I92" s="46"/>
-      <c r="J92" s="46"/>
+      <c r="I92" s="46">
+        <v>46150.791666666664</v>
+      </c>
+      <c r="J92" s="46">
+        <v>46150.895833333336</v>
+      </c>
       <c r="K92" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L92" s="47"/>
-      <c r="M92" s="47"/>
-      <c r="N92" s="45" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="L92" s="47">
+        <v>2</v>
+      </c>
+      <c r="M92" s="47">
+        <v>2</v>
+      </c>
+      <c r="N92" s="45">
         <f>IF(ISBLANK(L92), "", L92*VLOOKUP($F92,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O92" s="45" t="str">
+        <v>60</v>
+      </c>
+      <c r="O92" s="45">
         <f>IF(ISBLANK(M92), "", M92*VLOOKUP($F92,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P92" s="44"/>
+        <v>60</v>
+      </c>
+      <c r="P92" s="44" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B93" s="41">
@@ -10436,30 +11640,48 @@
       </c>
       <c r="C93" s="42" t="str">
         <f>IF(ISBLANK(D93), "", _xlfn.CONCAT("T", TEXT(B93, "0000"), "/", VLOOKUP(D93, Internal!$B$35:C$39, 2, FALSE), IF(OR(D93="QA", D93="Revision"), _xlfn.CONCAT("/", H93), "")))</f>
-        <v/>
-      </c>
-      <c r="D93" s="44"/>
-      <c r="E93" s="43"/>
-      <c r="F93" s="43"/>
-      <c r="G93" s="44"/>
+        <v>T0083/QA/</v>
+      </c>
+      <c r="D93" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E93" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F93" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G93" s="44" t="s">
+        <v>36</v>
+      </c>
       <c r="H93" s="43"/>
-      <c r="I93" s="46"/>
-      <c r="J93" s="46"/>
+      <c r="I93" s="46">
+        <v>46150.791666666664</v>
+      </c>
+      <c r="J93" s="46">
+        <v>46150.895833333336</v>
+      </c>
       <c r="K93" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L93" s="47"/>
-      <c r="M93" s="47"/>
-      <c r="N93" s="45" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="L93" s="47">
+        <v>2</v>
+      </c>
+      <c r="M93" s="47">
+        <v>2</v>
+      </c>
+      <c r="N93" s="45">
         <f>IF(ISBLANK(L93), "", L93*VLOOKUP($F93,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O93" s="45" t="str">
+        <v>60</v>
+      </c>
+      <c r="O93" s="45">
         <f>IF(ISBLANK(M93), "", M93*VLOOKUP($F93,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P93" s="44"/>
+        <v>60</v>
+      </c>
+      <c r="P93" s="44" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B94" s="41">
@@ -10467,30 +11689,48 @@
       </c>
       <c r="C94" s="42" t="str">
         <f>IF(ISBLANK(D94), "", _xlfn.CONCAT("T", TEXT(B94, "0000"), "/", VLOOKUP(D94, Internal!$B$35:C$39, 2, FALSE), IF(OR(D94="QA", D94="Revision"), _xlfn.CONCAT("/", H94), "")))</f>
-        <v/>
-      </c>
-      <c r="D94" s="44"/>
-      <c r="E94" s="43"/>
-      <c r="F94" s="43"/>
-      <c r="G94" s="44"/>
+        <v>T0084/QA/</v>
+      </c>
+      <c r="D94" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E94" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F94" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="44" t="s">
+        <v>45</v>
+      </c>
       <c r="H94" s="43"/>
-      <c r="I94" s="46"/>
-      <c r="J94" s="46"/>
+      <c r="I94" s="46">
+        <v>46150.791666666664</v>
+      </c>
+      <c r="J94" s="46">
+        <v>46150.895833333336</v>
+      </c>
       <c r="K94" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L94" s="47"/>
-      <c r="M94" s="47"/>
-      <c r="N94" s="45" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="L94" s="47">
+        <v>2</v>
+      </c>
+      <c r="M94" s="47">
+        <v>2</v>
+      </c>
+      <c r="N94" s="45">
         <f>IF(ISBLANK(L94), "", L94*VLOOKUP($F94,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O94" s="45" t="str">
+        <v>60</v>
+      </c>
+      <c r="O94" s="45">
         <f>IF(ISBLANK(M94), "", M94*VLOOKUP($F94,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P94" s="44"/>
+        <v>60</v>
+      </c>
+      <c r="P94" s="44" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B95" s="41">
@@ -10498,30 +11738,48 @@
       </c>
       <c r="C95" s="42" t="str">
         <f>IF(ISBLANK(D95), "", _xlfn.CONCAT("T", TEXT(B95, "0000"), "/", VLOOKUP(D95, Internal!$B$35:C$39, 2, FALSE), IF(OR(D95="QA", D95="Revision"), _xlfn.CONCAT("/", H95), "")))</f>
-        <v/>
-      </c>
-      <c r="D95" s="44"/>
-      <c r="E95" s="43"/>
-      <c r="F95" s="43"/>
-      <c r="G95" s="44"/>
+        <v>T0085/D</v>
+      </c>
+      <c r="D95" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E95" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F95" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="G95" s="44" t="s">
+        <v>46</v>
+      </c>
       <c r="H95" s="43"/>
-      <c r="I95" s="46"/>
-      <c r="J95" s="46"/>
+      <c r="I95" s="46">
+        <v>46150.916666666664</v>
+      </c>
+      <c r="J95" s="46">
+        <v>46150.9375</v>
+      </c>
       <c r="K95" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L95" s="47"/>
-      <c r="M95" s="47"/>
-      <c r="N95" s="45" t="str">
+        <v>Planned</v>
+      </c>
+      <c r="L95" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M95" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="N95" s="45">
         <f>IF(ISBLANK(L95), "", L95*VLOOKUP($F95,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O95" s="45" t="str">
+        <v>15</v>
+      </c>
+      <c r="O95" s="45">
         <f>IF(ISBLANK(M95), "", M95*VLOOKUP($F95,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P95" s="44"/>
+        <v>15</v>
+      </c>
+      <c r="P95" s="44" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B96" s="41">
@@ -10529,30 +11787,48 @@
       </c>
       <c r="C96" s="42" t="str">
         <f>IF(ISBLANK(D96), "", _xlfn.CONCAT("T", TEXT(B96, "0000"), "/", VLOOKUP(D96, Internal!$B$35:C$39, 2, FALSE), IF(OR(D96="QA", D96="Revision"), _xlfn.CONCAT("/", H96), "")))</f>
-        <v/>
-      </c>
-      <c r="D96" s="44"/>
-      <c r="E96" s="43"/>
-      <c r="F96" s="43"/>
-      <c r="G96" s="44"/>
+        <v>T0086/D</v>
+      </c>
+      <c r="D96" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E96" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F96" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="G96" s="44" t="s">
+        <v>47</v>
+      </c>
       <c r="H96" s="43"/>
-      <c r="I96" s="46"/>
-      <c r="J96" s="46"/>
+      <c r="I96" s="46">
+        <v>46150.9375</v>
+      </c>
+      <c r="J96" s="46">
+        <v>46150.951388888891</v>
+      </c>
       <c r="K96" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L96" s="47"/>
-      <c r="M96" s="47"/>
-      <c r="N96" s="45" t="str">
+        <v>Planned</v>
+      </c>
+      <c r="L96" s="47">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="M96" s="47">
+        <v>0.17</v>
+      </c>
+      <c r="N96" s="45">
         <f>IF(ISBLANK(L96), "", L96*VLOOKUP($F96,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O96" s="45" t="str">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="O96" s="45">
         <f>IF(ISBLANK(M96), "", M96*VLOOKUP($F96,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P96" s="44"/>
+        <v>5.1000000000000005</v>
+      </c>
+      <c r="P96" s="44" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B97" s="41">
@@ -10560,30 +11836,50 @@
       </c>
       <c r="C97" s="42" t="str">
         <f>IF(ISBLANK(D97), "", _xlfn.CONCAT("T", TEXT(B97, "0000"), "/", VLOOKUP(D97, Internal!$B$35:C$39, 2, FALSE), IF(OR(D97="QA", D97="Revision"), _xlfn.CONCAT("/", H97), "")))</f>
-        <v/>
-      </c>
-      <c r="D97" s="44"/>
-      <c r="E97" s="43"/>
-      <c r="F97" s="43"/>
-      <c r="G97" s="44"/>
-      <c r="H97" s="43"/>
-      <c r="I97" s="46"/>
-      <c r="J97" s="46"/>
+        <v>T0087/R/T0085/D</v>
+      </c>
+      <c r="D97" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E97" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F97" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="H97" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="I97" s="46">
+        <v>46150.951388888891</v>
+      </c>
+      <c r="J97" s="46">
+        <v>46150.96875</v>
+      </c>
       <c r="K97" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L97" s="47"/>
-      <c r="M97" s="47"/>
-      <c r="N97" s="45" t="str">
+        <v>Planned</v>
+      </c>
+      <c r="L97" s="47">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="M97" s="47">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="N97" s="45">
         <f>IF(ISBLANK(L97), "", L97*VLOOKUP($F97,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O97" s="45" t="str">
+        <v>12.479999999999999</v>
+      </c>
+      <c r="O97" s="45">
         <f>IF(ISBLANK(M97), "", M97*VLOOKUP($F97,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P97" s="44"/>
+        <v>12.479999999999999</v>
+      </c>
+      <c r="P97" s="44" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B98" s="41">
@@ -10591,30 +11887,50 @@
       </c>
       <c r="C98" s="42" t="str">
         <f>IF(ISBLANK(D98), "", _xlfn.CONCAT("T", TEXT(B98, "0000"), "/", VLOOKUP(D98, Internal!$B$35:C$39, 2, FALSE), IF(OR(D98="QA", D98="Revision"), _xlfn.CONCAT("/", H98), "")))</f>
-        <v/>
-      </c>
-      <c r="D98" s="44"/>
-      <c r="E98" s="43"/>
-      <c r="F98" s="43"/>
-      <c r="G98" s="44"/>
-      <c r="H98" s="43"/>
-      <c r="I98" s="46"/>
-      <c r="J98" s="46"/>
+        <v>T0088/R/T0085/D</v>
+      </c>
+      <c r="D98" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E98" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F98" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G98" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H98" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="I98" s="46">
+        <v>46150.951388888891</v>
+      </c>
+      <c r="J98" s="46">
+        <v>46150.96875</v>
+      </c>
       <c r="K98" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L98" s="47"/>
-      <c r="M98" s="47"/>
-      <c r="N98" s="45" t="str">
+        <v>Planned</v>
+      </c>
+      <c r="L98" s="47">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="M98" s="47">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="N98" s="45">
         <f>IF(ISBLANK(L98), "", L98*VLOOKUP($F98,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O98" s="45" t="str">
+        <v>20.8</v>
+      </c>
+      <c r="O98" s="45">
         <f>IF(ISBLANK(M98), "", M98*VLOOKUP($F98,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P98" s="44"/>
+        <v>20.8</v>
+      </c>
+      <c r="P98" s="44" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B99" s="41">
@@ -10998,12 +12314,12 @@
     <mergeCell ref="I9:J9"/>
   </mergeCells>
   <conditionalFormatting sqref="H11:H110">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11:J110">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="J11:J77 J79:J110">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11055,7 +12371,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>J11:J110</xm:sqref>
+          <xm:sqref>J11:J77 J79:J110</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Start moment" prompt="Indicate the moment when the assignee starts working on this task.  Use format yy/mm/dd hh:mm." xr:uid="{175B319B-7D79-46C0-980E-ECB0D923AF19}">
           <x14:formula1>
@@ -11064,7 +12380,7 @@
           <x14:formula2>
             <xm:f>Internal!$C$23</xm:f>
           </x14:formula2>
-          <xm:sqref>I11:I110</xm:sqref>
+          <xm:sqref>J78 I11:I110</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -11082,40 +12398,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="59"/>
-      <c r="L4" s="59"/>
-      <c r="M4" s="59"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="59"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="5"/>
@@ -11134,7 +12450,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="58" t="s">
         <v>68</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -11157,7 +12473,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C7" s="56"/>
+      <c r="C7" s="58"/>
       <c r="D7" s="11" t="s">
         <v>70</v>
       </c>
@@ -11175,19 +12491,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="57"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="57" t="s">
+      <c r="L9" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57" t="s">
+      <c r="M9" s="59"/>
+      <c r="N9" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="O9" s="57"/>
+      <c r="O9" s="59"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -14430,52 +15746,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="5"/>
